--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="169">
   <si>
     <t>Materia</t>
   </si>
@@ -1017,10 +1017,10 @@
         <v>-1</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -1071,10 +1071,10 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1094,10 +1094,10 @@
         <v>-1</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>6</v>
@@ -1148,10 +1148,10 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>6</v>
@@ -1171,10 +1171,10 @@
         <v>-1</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F6">
         <v>10</v>
@@ -1225,10 +1225,10 @@
         <v>-1</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>10</v>
@@ -1248,10 +1248,10 @@
         <v>-1</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -1302,10 +1302,10 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1325,10 +1325,10 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1379,10 +1379,10 @@
         <v>-1</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1402,10 +1402,10 @@
         <v>-1</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F9">
         <v>9</v>
@@ -1456,10 +1456,10 @@
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1479,10 +1479,10 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -1533,10 +1533,10 @@
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1556,10 +1556,10 @@
         <v>-1</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -1610,10 +1610,10 @@
         <v>-1</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1633,10 +1633,10 @@
         <v>-1</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F12">
         <v>8</v>
@@ -1687,10 +1687,10 @@
         <v>-1</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1710,10 +1710,10 @@
         <v>-1</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>10</v>
@@ -1764,10 +1764,10 @@
         <v>-1</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>10</v>
@@ -1787,10 +1787,10 @@
         <v>-1</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F14">
         <v>6</v>
@@ -1841,10 +1841,10 @@
         <v>-1</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1864,10 +1864,10 @@
         <v>-1</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F15">
         <v>8</v>
@@ -1918,10 +1918,10 @@
         <v>-1</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1941,10 +1941,10 @@
         <v>-1</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -1995,10 +1995,10 @@
         <v>-1</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -2018,10 +2018,10 @@
         <v>-1</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -2072,10 +2072,10 @@
         <v>-1</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -2095,10 +2095,10 @@
         <v>-1</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F18">
         <v>8</v>
@@ -2149,10 +2149,10 @@
         <v>-1</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2172,10 +2172,10 @@
         <v>-1</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2226,10 +2226,10 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
         <v>5</v>
@@ -2249,10 +2249,10 @@
         <v>-1</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2303,10 +2303,10 @@
         <v>-1</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2326,10 +2326,10 @@
         <v>-1</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F21">
         <v>8</v>
@@ -2380,10 +2380,10 @@
         <v>-1</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2403,10 +2403,10 @@
         <v>-1</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2457,10 +2457,10 @@
         <v>-1</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2480,10 +2480,10 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2534,10 +2534,10 @@
         <v>-1</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2557,10 +2557,10 @@
         <v>-1</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F24">
         <v>10</v>
@@ -2611,10 +2611,10 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2634,10 +2634,10 @@
         <v>-1</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F25">
         <v>5</v>
@@ -2688,10 +2688,10 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2711,10 +2711,10 @@
         <v>-1</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F26">
         <v>10</v>
@@ -2765,10 +2765,10 @@
         <v>-1</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2788,10 +2788,10 @@
         <v>-1</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -2842,10 +2842,10 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>6</v>
@@ -2865,10 +2865,10 @@
         <v>-1</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -2919,10 +2919,10 @@
         <v>-1</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2942,10 +2942,10 @@
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>9</v>
@@ -2996,10 +2996,10 @@
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3019,10 +3019,10 @@
         <v>-1</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>5</v>
@@ -3073,10 +3073,10 @@
         <v>-1</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3096,10 +3096,10 @@
         <v>-1</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F31">
         <v>8</v>
@@ -3150,10 +3150,10 @@
         <v>-1</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3173,10 +3173,10 @@
         <v>-1</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F32">
         <v>5</v>
@@ -3227,10 +3227,10 @@
         <v>-1</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3250,10 +3250,10 @@
         <v>-1</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3304,10 +3304,10 @@
         <v>-1</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3327,10 +3327,10 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F34">
         <v>10</v>
@@ -3381,10 +3381,10 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X34">
         <v>10</v>
@@ -3404,10 +3404,10 @@
         <v>-1</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F35">
         <v>10</v>
@@ -3458,10 +3458,10 @@
         <v>-1</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3481,10 +3481,10 @@
         <v>-1</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F36">
         <v>10</v>
@@ -3535,10 +3535,10 @@
         <v>-1</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3558,10 +3558,10 @@
         <v>-1</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F37">
         <v>10</v>
@@ -3612,10 +3612,10 @@
         <v>-1</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3635,10 +3635,10 @@
         <v>-1</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F38">
         <v>6</v>
@@ -3689,10 +3689,10 @@
         <v>-1</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X38">
         <v>6</v>
@@ -3712,10 +3712,10 @@
         <v>-1</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -3766,10 +3766,10 @@
         <v>-1</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X39">
         <v>10</v>
@@ -3789,10 +3789,10 @@
         <v>-1</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -3843,10 +3843,10 @@
         <v>-1</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3866,10 +3866,10 @@
         <v>-1</v>
       </c>
       <c r="D41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F41">
         <v>10</v>
@@ -3920,10 +3920,10 @@
         <v>-1</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X41">
         <v>10</v>
@@ -3943,10 +3943,10 @@
         <v>-1</v>
       </c>
       <c r="D42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F42">
         <v>10</v>
@@ -3997,10 +3997,10 @@
         <v>-1</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -4020,10 +4020,10 @@
         <v>-1</v>
       </c>
       <c r="D43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F43">
         <v>5</v>
@@ -4074,10 +4074,10 @@
         <v>-1</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X43">
         <v>5</v>
@@ -4207,10 +4207,10 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -4266,10 +4266,10 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>80</v>
@@ -4325,10 +4325,10 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>95</v>
@@ -4384,10 +4384,10 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>85</v>
@@ -4443,10 +4443,10 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -4502,10 +4502,10 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -4561,10 +4561,10 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>85</v>
@@ -4620,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>95</v>
@@ -4738,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>90</v>
@@ -4797,10 +4797,10 @@
         <v>0</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>80</v>
@@ -4856,10 +4856,10 @@
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>80</v>
@@ -4915,10 +4915,10 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>95</v>
@@ -4974,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>80</v>
@@ -5033,10 +5033,10 @@
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>85</v>
@@ -5151,10 +5151,10 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>90</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>95</v>
@@ -5328,10 +5328,10 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>85</v>
@@ -5387,10 +5387,10 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>95</v>
@@ -5446,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>80</v>
@@ -5505,10 +5505,10 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="F27">
         <v>75</v>
@@ -5623,10 +5623,10 @@
         <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="F28">
         <v>20</v>
@@ -5682,10 +5682,10 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -5741,10 +5741,10 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>40</v>
@@ -5800,10 +5800,10 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>80</v>
@@ -5859,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -5918,10 +5918,10 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>95</v>
@@ -5977,10 +5977,10 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -6036,10 +6036,10 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F35">
         <v>95</v>
@@ -6095,10 +6095,10 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F36">
         <v>100</v>
@@ -6154,10 +6154,10 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F37">
         <v>100</v>
@@ -6213,10 +6213,10 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F38">
         <v>90</v>
@@ -6272,10 +6272,10 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F39">
         <v>100</v>
@@ -6331,10 +6331,10 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F40">
         <v>100</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F41">
         <v>100</v>
@@ -6449,10 +6449,10 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F42">
         <v>100</v>
@@ -6508,10 +6508,10 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43">
         <v>85</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -6637,7 +6637,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6646,27 +6646,30 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>8.199999999999999</v>
       </c>
       <c r="I3">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6675,27 +6678,30 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>12.5</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
       <c r="I4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6704,19 +6710,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="G5">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6727,7 +6733,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6736,19 +6742,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6759,7 +6765,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6768,19 +6774,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="G7">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6796,7 +6802,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6837,7 +6843,7 @@
         <v>129</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
@@ -6845,19 +6851,19 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>22330051920052</v>
+        <v>22330051920333</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -6865,16 +6871,16 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>22330051920052</v>
+        <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6885,19 +6891,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>22330051920333</v>
+        <v>22330051920054</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>64</v>
@@ -6905,19 +6911,19 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>22330051920333</v>
+        <v>22330051920055</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -6925,16 +6931,16 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>22330051920333</v>
+        <v>22330051920208</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -6945,19 +6951,19 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>22330051920053</v>
+        <v>22330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>
@@ -6965,19 +6971,19 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920053</v>
+        <v>22330051920058</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>64</v>
@@ -6985,16 +6991,16 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920053</v>
+        <v>22330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -7005,19 +7011,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920054</v>
+        <v>22330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>64</v>
@@ -7025,19 +7031,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920054</v>
+        <v>22330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
         <v>64</v>
@@ -7045,16 +7051,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920054</v>
+        <v>22330051920060</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
@@ -7065,19 +7071,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920055</v>
+        <v>22330051920063</v>
       </c>
       <c r="B14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
         <v>64</v>
@@ -7085,19 +7091,19 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920055</v>
+        <v>22330051920212</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>64</v>
@@ -7105,16 +7111,16 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920055</v>
+        <v>22330051920064</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7125,19 +7131,19 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920208</v>
+        <v>22330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>64</v>
@@ -7145,19 +7151,19 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920208</v>
+        <v>22330051920066</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>64</v>
@@ -7165,16 +7171,16 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920208</v>
+        <v>22330051920316</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D19" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -7185,19 +7191,19 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920057</v>
+        <v>22330051920334</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>64</v>
@@ -7205,19 +7211,19 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>22330051920057</v>
+        <v>22230030070114</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
         <v>64</v>
@@ -7225,16 +7231,16 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>22330051920057</v>
+        <v>22330051920067</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -7245,19 +7251,19 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>22330051920058</v>
+        <v>22330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
         <v>64</v>
@@ -7265,19 +7271,19 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>22330051920058</v>
+        <v>22330051920380</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
         <v>64</v>
@@ -7285,16 +7291,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>22330051920058</v>
+        <v>22330051920068</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -7305,19 +7311,19 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>22330051920059</v>
+        <v>22330051920069</v>
       </c>
       <c r="B26" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C26" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>64</v>
@@ -7325,19 +7331,19 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>22330051920059</v>
+        <v>22330051920070</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F27" t="s">
         <v>64</v>
@@ -7345,16 +7351,16 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>22330051920059</v>
+        <v>22330051920071</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E28" t="s">
         <v>6</v>
@@ -7365,19 +7371,19 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>22330051920061</v>
+        <v>22330051920317</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F29" t="s">
         <v>64</v>
@@ -7385,19 +7391,19 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>22330051920061</v>
+        <v>22330051920072</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="E30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
@@ -7405,16 +7411,16 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>22330051920061</v>
+        <v>22330051920073</v>
       </c>
       <c r="B31" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E31" t="s">
         <v>6</v>
@@ -7425,19 +7431,19 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>22330051920062</v>
+        <v>22330051920075</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C32" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
         <v>64</v>
@@ -7445,19 +7451,19 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>22330051920062</v>
+        <v>22330051920076</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C33" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>64</v>
@@ -7465,16 +7471,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>22330051920062</v>
+        <v>22330051920077</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E34" t="s">
         <v>6</v>
@@ -7485,19 +7491,19 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>22330051920060</v>
+        <v>22330051920078</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
         <v>64</v>
@@ -7505,19 +7511,19 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>22330051920060</v>
+        <v>22330051920081</v>
       </c>
       <c r="B36" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C36" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="E36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F36" t="s">
         <v>64</v>
@@ -7525,16 +7531,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>22330051920060</v>
+        <v>22330051920079</v>
       </c>
       <c r="B37" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="D37" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
         <v>6</v>
@@ -7545,19 +7551,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>22330051920063</v>
+        <v>22330051920080</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F38" t="s">
         <v>64</v>
@@ -7565,19 +7571,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>22330051920063</v>
+        <v>22330051920082</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C39" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D39" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="E39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F39" t="s">
         <v>64</v>
@@ -7585,16 +7591,16 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>22330051920063</v>
+        <v>22330051920083</v>
       </c>
       <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="C40" t="s">
-        <v>111</v>
-      </c>
       <c r="D40" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="E40" t="s">
         <v>6</v>
@@ -7605,1621 +7611,21 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>22330051920212</v>
+        <v>22330051920084</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F41" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920212</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" t="s">
-        <v>112</v>
-      </c>
-      <c r="D42" t="s">
-        <v>142</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920212</v>
-      </c>
-      <c r="B43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" t="s">
-        <v>112</v>
-      </c>
-      <c r="D43" t="s">
-        <v>142</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920064</v>
-      </c>
-      <c r="B44" t="s">
-        <v>81</v>
-      </c>
-      <c r="C44" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" t="s">
-        <v>143</v>
-      </c>
-      <c r="E44" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920064</v>
-      </c>
-      <c r="B45" t="s">
-        <v>81</v>
-      </c>
-      <c r="C45" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" t="s">
-        <v>143</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920064</v>
-      </c>
-      <c r="B46" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" t="s">
-        <v>143</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920065</v>
-      </c>
-      <c r="B47" t="s">
-        <v>81</v>
-      </c>
-      <c r="C47" t="s">
-        <v>114</v>
-      </c>
-      <c r="D47" t="s">
-        <v>144</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920065</v>
-      </c>
-      <c r="B48" t="s">
-        <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" t="s">
-        <v>144</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920065</v>
-      </c>
-      <c r="B49" t="s">
-        <v>81</v>
-      </c>
-      <c r="C49" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" t="s">
-        <v>144</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920066</v>
-      </c>
-      <c r="B50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" t="s">
-        <v>115</v>
-      </c>
-      <c r="D50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920066</v>
-      </c>
-      <c r="B51" t="s">
-        <v>81</v>
-      </c>
-      <c r="C51" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" t="s">
-        <v>145</v>
-      </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920066</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" t="s">
-        <v>145</v>
-      </c>
-      <c r="E52" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920316</v>
-      </c>
-      <c r="B53" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" t="s">
-        <v>146</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920316</v>
-      </c>
-      <c r="B54" t="s">
-        <v>82</v>
-      </c>
-      <c r="C54" t="s">
-        <v>116</v>
-      </c>
-      <c r="D54" t="s">
-        <v>146</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920316</v>
-      </c>
-      <c r="B55" t="s">
-        <v>82</v>
-      </c>
-      <c r="C55" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" t="s">
-        <v>146</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920334</v>
-      </c>
-      <c r="B56" t="s">
-        <v>83</v>
-      </c>
-      <c r="C56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" t="s">
-        <v>147</v>
-      </c>
-      <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920334</v>
-      </c>
-      <c r="B57" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" t="s">
-        <v>147</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920334</v>
-      </c>
-      <c r="B58" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>147</v>
-      </c>
-      <c r="E58" t="s">
-        <v>6</v>
-      </c>
-      <c r="F58" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22230030070114</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>117</v>
-      </c>
-      <c r="D59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22230030070114</v>
-      </c>
-      <c r="B60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" t="s">
-        <v>117</v>
-      </c>
-      <c r="D60" t="s">
-        <v>148</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22230030070114</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>117</v>
-      </c>
-      <c r="D61" t="s">
-        <v>148</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920067</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" t="s">
-        <v>149</v>
-      </c>
-      <c r="E62" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920067</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D63" t="s">
-        <v>149</v>
-      </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920067</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>118</v>
-      </c>
-      <c r="D64" t="s">
-        <v>149</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920335</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>119</v>
-      </c>
-      <c r="D65" t="s">
-        <v>150</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920335</v>
-      </c>
-      <c r="B66" t="s">
-        <v>86</v>
-      </c>
-      <c r="C66" t="s">
-        <v>119</v>
-      </c>
-      <c r="D66" t="s">
-        <v>150</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920335</v>
-      </c>
-      <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" t="s">
-        <v>119</v>
-      </c>
-      <c r="D67" t="s">
-        <v>150</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920380</v>
-      </c>
-      <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" t="s">
-        <v>120</v>
-      </c>
-      <c r="D68" t="s">
-        <v>151</v>
-      </c>
-      <c r="E68" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920380</v>
-      </c>
-      <c r="B69" t="s">
-        <v>87</v>
-      </c>
-      <c r="C69" t="s">
-        <v>120</v>
-      </c>
-      <c r="D69" t="s">
-        <v>151</v>
-      </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920380</v>
-      </c>
-      <c r="B70" t="s">
-        <v>87</v>
-      </c>
-      <c r="C70" t="s">
-        <v>120</v>
-      </c>
-      <c r="D70" t="s">
-        <v>151</v>
-      </c>
-      <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920068</v>
-      </c>
-      <c r="B71" t="s">
-        <v>88</v>
-      </c>
-      <c r="C71" t="s">
-        <v>114</v>
-      </c>
-      <c r="D71" t="s">
-        <v>152</v>
-      </c>
-      <c r="E71" t="s">
-        <v>8</v>
-      </c>
-      <c r="F71" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920068</v>
-      </c>
-      <c r="B72" t="s">
-        <v>88</v>
-      </c>
-      <c r="C72" t="s">
-        <v>114</v>
-      </c>
-      <c r="D72" t="s">
-        <v>152</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920068</v>
-      </c>
-      <c r="B73" t="s">
-        <v>88</v>
-      </c>
-      <c r="C73" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" t="s">
-        <v>152</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920069</v>
-      </c>
-      <c r="B74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" t="s">
-        <v>121</v>
-      </c>
-      <c r="D74" t="s">
-        <v>153</v>
-      </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920069</v>
-      </c>
-      <c r="B75" t="s">
-        <v>87</v>
-      </c>
-      <c r="C75" t="s">
-        <v>121</v>
-      </c>
-      <c r="D75" t="s">
-        <v>153</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>22330051920069</v>
-      </c>
-      <c r="B76" t="s">
-        <v>87</v>
-      </c>
-      <c r="C76" t="s">
-        <v>121</v>
-      </c>
-      <c r="D76" t="s">
-        <v>153</v>
-      </c>
-      <c r="E76" t="s">
-        <v>6</v>
-      </c>
-      <c r="F76" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>22330051920070</v>
-      </c>
-      <c r="B77" t="s">
-        <v>89</v>
-      </c>
-      <c r="C77" t="s">
-        <v>122</v>
-      </c>
-      <c r="D77" t="s">
-        <v>154</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>22330051920070</v>
-      </c>
-      <c r="B78" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" t="s">
-        <v>122</v>
-      </c>
-      <c r="D78" t="s">
-        <v>154</v>
-      </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>22330051920070</v>
-      </c>
-      <c r="B79" t="s">
-        <v>89</v>
-      </c>
-      <c r="C79" t="s">
-        <v>122</v>
-      </c>
-      <c r="D79" t="s">
-        <v>154</v>
-      </c>
-      <c r="E79" t="s">
-        <v>6</v>
-      </c>
-      <c r="F79" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>22330051920071</v>
-      </c>
-      <c r="B80" t="s">
-        <v>90</v>
-      </c>
-      <c r="C80" t="s">
-        <v>123</v>
-      </c>
-      <c r="D80" t="s">
-        <v>155</v>
-      </c>
-      <c r="E80" t="s">
-        <v>8</v>
-      </c>
-      <c r="F80" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>22330051920071</v>
-      </c>
-      <c r="B81" t="s">
-        <v>90</v>
-      </c>
-      <c r="C81" t="s">
-        <v>123</v>
-      </c>
-      <c r="D81" t="s">
-        <v>155</v>
-      </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>22330051920071</v>
-      </c>
-      <c r="B82" t="s">
-        <v>90</v>
-      </c>
-      <c r="C82" t="s">
-        <v>123</v>
-      </c>
-      <c r="D82" t="s">
-        <v>155</v>
-      </c>
-      <c r="E82" t="s">
-        <v>6</v>
-      </c>
-      <c r="F82" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>22330051920317</v>
-      </c>
-      <c r="B83" t="s">
-        <v>91</v>
-      </c>
-      <c r="C83" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" t="s">
-        <v>156</v>
-      </c>
-      <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>22330051920317</v>
-      </c>
-      <c r="B84" t="s">
-        <v>91</v>
-      </c>
-      <c r="C84" t="s">
-        <v>80</v>
-      </c>
-      <c r="D84" t="s">
-        <v>156</v>
-      </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>22330051920317</v>
-      </c>
-      <c r="B85" t="s">
-        <v>91</v>
-      </c>
-      <c r="C85" t="s">
-        <v>80</v>
-      </c>
-      <c r="D85" t="s">
-        <v>156</v>
-      </c>
-      <c r="E85" t="s">
-        <v>6</v>
-      </c>
-      <c r="F85" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>22330051920072</v>
-      </c>
-      <c r="B86" t="s">
-        <v>92</v>
-      </c>
-      <c r="C86" t="s">
-        <v>124</v>
-      </c>
-      <c r="D86" t="s">
-        <v>157</v>
-      </c>
-      <c r="E86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>22330051920072</v>
-      </c>
-      <c r="B87" t="s">
-        <v>92</v>
-      </c>
-      <c r="C87" t="s">
-        <v>124</v>
-      </c>
-      <c r="D87" t="s">
-        <v>157</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>22330051920072</v>
-      </c>
-      <c r="B88" t="s">
-        <v>92</v>
-      </c>
-      <c r="C88" t="s">
-        <v>124</v>
-      </c>
-      <c r="D88" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" t="s">
-        <v>6</v>
-      </c>
-      <c r="F88" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>22330051920073</v>
-      </c>
-      <c r="B89" t="s">
-        <v>93</v>
-      </c>
-      <c r="C89" t="s">
-        <v>114</v>
-      </c>
-      <c r="D89" t="s">
-        <v>158</v>
-      </c>
-      <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>22330051920073</v>
-      </c>
-      <c r="B90" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" t="s">
-        <v>114</v>
-      </c>
-      <c r="D90" t="s">
-        <v>158</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>22330051920073</v>
-      </c>
-      <c r="B91" t="s">
-        <v>93</v>
-      </c>
-      <c r="C91" t="s">
-        <v>114</v>
-      </c>
-      <c r="D91" t="s">
-        <v>158</v>
-      </c>
-      <c r="E91" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>22330051920075</v>
-      </c>
-      <c r="B92" t="s">
-        <v>94</v>
-      </c>
-      <c r="C92" t="s">
-        <v>125</v>
-      </c>
-      <c r="D92" t="s">
-        <v>159</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>22330051920075</v>
-      </c>
-      <c r="B93" t="s">
-        <v>94</v>
-      </c>
-      <c r="C93" t="s">
-        <v>125</v>
-      </c>
-      <c r="D93" t="s">
-        <v>159</v>
-      </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>22330051920075</v>
-      </c>
-      <c r="B94" t="s">
-        <v>94</v>
-      </c>
-      <c r="C94" t="s">
-        <v>125</v>
-      </c>
-      <c r="D94" t="s">
-        <v>159</v>
-      </c>
-      <c r="E94" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>22330051920076</v>
-      </c>
-      <c r="B95" t="s">
-        <v>94</v>
-      </c>
-      <c r="C95" t="s">
-        <v>99</v>
-      </c>
-      <c r="D95" t="s">
-        <v>160</v>
-      </c>
-      <c r="E95" t="s">
-        <v>8</v>
-      </c>
-      <c r="F95" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>22330051920076</v>
-      </c>
-      <c r="B96" t="s">
-        <v>94</v>
-      </c>
-      <c r="C96" t="s">
-        <v>99</v>
-      </c>
-      <c r="D96" t="s">
-        <v>160</v>
-      </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>22330051920076</v>
-      </c>
-      <c r="B97" t="s">
-        <v>94</v>
-      </c>
-      <c r="C97" t="s">
-        <v>99</v>
-      </c>
-      <c r="D97" t="s">
-        <v>160</v>
-      </c>
-      <c r="E97" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>22330051920077</v>
-      </c>
-      <c r="B98" t="s">
-        <v>95</v>
-      </c>
-      <c r="C98" t="s">
-        <v>97</v>
-      </c>
-      <c r="D98" t="s">
-        <v>161</v>
-      </c>
-      <c r="E98" t="s">
-        <v>8</v>
-      </c>
-      <c r="F98" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>22330051920077</v>
-      </c>
-      <c r="B99" t="s">
-        <v>95</v>
-      </c>
-      <c r="C99" t="s">
-        <v>97</v>
-      </c>
-      <c r="D99" t="s">
-        <v>161</v>
-      </c>
-      <c r="E99" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>22330051920077</v>
-      </c>
-      <c r="B100" t="s">
-        <v>95</v>
-      </c>
-      <c r="C100" t="s">
-        <v>97</v>
-      </c>
-      <c r="D100" t="s">
-        <v>161</v>
-      </c>
-      <c r="E100" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>22330051920078</v>
-      </c>
-      <c r="B101" t="s">
-        <v>96</v>
-      </c>
-      <c r="C101" t="s">
-        <v>126</v>
-      </c>
-      <c r="D101" t="s">
-        <v>162</v>
-      </c>
-      <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>22330051920078</v>
-      </c>
-      <c r="B102" t="s">
-        <v>96</v>
-      </c>
-      <c r="C102" t="s">
-        <v>126</v>
-      </c>
-      <c r="D102" t="s">
-        <v>162</v>
-      </c>
-      <c r="E102" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>22330051920078</v>
-      </c>
-      <c r="B103" t="s">
-        <v>96</v>
-      </c>
-      <c r="C103" t="s">
-        <v>126</v>
-      </c>
-      <c r="D103" t="s">
-        <v>162</v>
-      </c>
-      <c r="E103" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>22330051920081</v>
-      </c>
-      <c r="B104" t="s">
-        <v>97</v>
-      </c>
-      <c r="C104" t="s">
-        <v>127</v>
-      </c>
-      <c r="D104" t="s">
-        <v>163</v>
-      </c>
-      <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>22330051920081</v>
-      </c>
-      <c r="B105" t="s">
-        <v>97</v>
-      </c>
-      <c r="C105" t="s">
-        <v>127</v>
-      </c>
-      <c r="D105" t="s">
-        <v>163</v>
-      </c>
-      <c r="E105" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>22330051920081</v>
-      </c>
-      <c r="B106" t="s">
-        <v>97</v>
-      </c>
-      <c r="C106" t="s">
-        <v>127</v>
-      </c>
-      <c r="D106" t="s">
-        <v>163</v>
-      </c>
-      <c r="E106" t="s">
-        <v>6</v>
-      </c>
-      <c r="F106" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>22330051920079</v>
-      </c>
-      <c r="B107" t="s">
-        <v>96</v>
-      </c>
-      <c r="C107" t="s">
-        <v>77</v>
-      </c>
-      <c r="D107" t="s">
-        <v>164</v>
-      </c>
-      <c r="E107" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>22330051920079</v>
-      </c>
-      <c r="B108" t="s">
-        <v>96</v>
-      </c>
-      <c r="C108" t="s">
-        <v>77</v>
-      </c>
-      <c r="D108" t="s">
-        <v>164</v>
-      </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>22330051920079</v>
-      </c>
-      <c r="B109" t="s">
-        <v>96</v>
-      </c>
-      <c r="C109" t="s">
-        <v>77</v>
-      </c>
-      <c r="D109" t="s">
-        <v>164</v>
-      </c>
-      <c r="E109" t="s">
-        <v>6</v>
-      </c>
-      <c r="F109" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>22330051920080</v>
-      </c>
-      <c r="B110" t="s">
-        <v>98</v>
-      </c>
-      <c r="C110" t="s">
-        <v>101</v>
-      </c>
-      <c r="D110" t="s">
-        <v>165</v>
-      </c>
-      <c r="E110" t="s">
-        <v>8</v>
-      </c>
-      <c r="F110" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>22330051920080</v>
-      </c>
-      <c r="B111" t="s">
-        <v>98</v>
-      </c>
-      <c r="C111" t="s">
-        <v>101</v>
-      </c>
-      <c r="D111" t="s">
-        <v>165</v>
-      </c>
-      <c r="E111" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>22330051920080</v>
-      </c>
-      <c r="B112" t="s">
-        <v>98</v>
-      </c>
-      <c r="C112" t="s">
-        <v>101</v>
-      </c>
-      <c r="D112" t="s">
-        <v>165</v>
-      </c>
-      <c r="E112" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>22330051920082</v>
-      </c>
-      <c r="B113" t="s">
-        <v>99</v>
-      </c>
-      <c r="C113" t="s">
-        <v>128</v>
-      </c>
-      <c r="D113" t="s">
-        <v>166</v>
-      </c>
-      <c r="E113" t="s">
-        <v>8</v>
-      </c>
-      <c r="F113" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>22330051920082</v>
-      </c>
-      <c r="B114" t="s">
-        <v>99</v>
-      </c>
-      <c r="C114" t="s">
-        <v>128</v>
-      </c>
-      <c r="D114" t="s">
-        <v>166</v>
-      </c>
-      <c r="E114" t="s">
-        <v>7</v>
-      </c>
-      <c r="F114" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>22330051920082</v>
-      </c>
-      <c r="B115" t="s">
-        <v>99</v>
-      </c>
-      <c r="C115" t="s">
-        <v>128</v>
-      </c>
-      <c r="D115" t="s">
-        <v>166</v>
-      </c>
-      <c r="E115" t="s">
-        <v>6</v>
-      </c>
-      <c r="F115" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>22330051920083</v>
-      </c>
-      <c r="B116" t="s">
-        <v>100</v>
-      </c>
-      <c r="C116" t="s">
-        <v>78</v>
-      </c>
-      <c r="D116" t="s">
-        <v>167</v>
-      </c>
-      <c r="E116" t="s">
-        <v>8</v>
-      </c>
-      <c r="F116" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>22330051920083</v>
-      </c>
-      <c r="B117" t="s">
-        <v>100</v>
-      </c>
-      <c r="C117" t="s">
-        <v>78</v>
-      </c>
-      <c r="D117" t="s">
-        <v>167</v>
-      </c>
-      <c r="E117" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>22330051920083</v>
-      </c>
-      <c r="B118" t="s">
-        <v>100</v>
-      </c>
-      <c r="C118" t="s">
-        <v>78</v>
-      </c>
-      <c r="D118" t="s">
-        <v>167</v>
-      </c>
-      <c r="E118" t="s">
-        <v>6</v>
-      </c>
-      <c r="F118" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>22330051920084</v>
-      </c>
-      <c r="B119" t="s">
-        <v>101</v>
-      </c>
-      <c r="C119" t="s">
-        <v>115</v>
-      </c>
-      <c r="D119" t="s">
-        <v>168</v>
-      </c>
-      <c r="E119" t="s">
-        <v>8</v>
-      </c>
-      <c r="F119" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>22330051920084</v>
-      </c>
-      <c r="B120" t="s">
-        <v>101</v>
-      </c>
-      <c r="C120" t="s">
-        <v>115</v>
-      </c>
-      <c r="D120" t="s">
-        <v>168</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>22330051920084</v>
-      </c>
-      <c r="B121" t="s">
-        <v>101</v>
-      </c>
-      <c r="C121" t="s">
-        <v>115</v>
-      </c>
-      <c r="D121" t="s">
-        <v>168</v>
-      </c>
-      <c r="E121" t="s">
-        <v>6</v>
-      </c>
-      <c r="F121" t="s">
         <v>64</v>
       </c>
     </row>
@@ -9268,7 +7674,7 @@
         <v>129</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -9285,7 +7691,7 @@
         <v>130</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -9302,7 +7708,7 @@
         <v>131</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -9319,7 +7725,7 @@
         <v>132</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9336,7 +7742,7 @@
         <v>133</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -9353,7 +7759,7 @@
         <v>134</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9370,7 +7776,7 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -9387,7 +7793,7 @@
         <v>136</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -9404,7 +7810,7 @@
         <v>137</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -9421,7 +7827,7 @@
         <v>138</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -9438,7 +7844,7 @@
         <v>139</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -9455,7 +7861,7 @@
         <v>140</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -9472,7 +7878,7 @@
         <v>141</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -9489,7 +7895,7 @@
         <v>142</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -9506,7 +7912,7 @@
         <v>143</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -9523,7 +7929,7 @@
         <v>144</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -9540,7 +7946,7 @@
         <v>145</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9557,7 +7963,7 @@
         <v>146</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9574,7 +7980,7 @@
         <v>147</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9591,7 +7997,7 @@
         <v>148</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9608,7 +8014,7 @@
         <v>149</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9625,7 +8031,7 @@
         <v>150</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9642,7 +8048,7 @@
         <v>151</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9659,7 +8065,7 @@
         <v>152</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9676,7 +8082,7 @@
         <v>153</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -9693,7 +8099,7 @@
         <v>154</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9710,7 +8116,7 @@
         <v>155</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -9727,7 +8133,7 @@
         <v>156</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -9744,7 +8150,7 @@
         <v>157</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -9761,7 +8167,7 @@
         <v>158</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -9778,7 +8184,7 @@
         <v>159</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -9795,7 +8201,7 @@
         <v>160</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9812,7 +8218,7 @@
         <v>161</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -9829,7 +8235,7 @@
         <v>162</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -9846,7 +8252,7 @@
         <v>163</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9863,7 +8269,7 @@
         <v>164</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -9880,7 +8286,7 @@
         <v>165</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -9897,7 +8303,7 @@
         <v>166</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -9914,7 +8320,7 @@
         <v>167</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -9931,7 +8337,7 @@
         <v>168</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9941,7 +8347,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -9971,6 +8377,949 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920333</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920333</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920212</v>
+      </c>
+      <c r="B4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" t="s">
+        <v>112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920212</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920068</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920068</v>
+      </c>
+      <c r="B7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920070</v>
+      </c>
+      <c r="B8" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920070</v>
+      </c>
+      <c r="B9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920071</v>
+      </c>
+      <c r="B10" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920071</v>
+      </c>
+      <c r="B11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" t="s">
+        <v>155</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920052</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920053</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920054</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920055</v>
+      </c>
+      <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920208</v>
+      </c>
+      <c r="B16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920057</v>
+      </c>
+      <c r="B17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920058</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>136</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920059</v>
+      </c>
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920061</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920062</v>
+      </c>
+      <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920060</v>
+      </c>
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920063</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920064</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>113</v>
+      </c>
+      <c r="D24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E24" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" t="s">
+        <v>64</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920066</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920316</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>22330051920334</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D27" t="s">
+        <v>147</v>
+      </c>
+      <c r="E27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>64</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22230030070114</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920067</v>
+      </c>
+      <c r="B29" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" t="s">
+        <v>150</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>64</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920380</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>151</v>
+      </c>
+      <c r="E31" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" t="s">
+        <v>64</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>22330051920317</v>
+      </c>
+      <c r="B32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22330051920073</v>
+      </c>
+      <c r="B33" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" t="s">
+        <v>158</v>
+      </c>
+      <c r="E33" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" t="s">
+        <v>64</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>22330051920075</v>
+      </c>
+      <c r="B34" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>159</v>
+      </c>
+      <c r="E34" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>22330051920076</v>
+      </c>
+      <c r="B35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+      <c r="D35" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>22330051920077</v>
+      </c>
+      <c r="B36" t="s">
+        <v>95</v>
+      </c>
+      <c r="C36" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" t="s">
+        <v>64</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>22330051920078</v>
+      </c>
+      <c r="B37" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" t="s">
+        <v>126</v>
+      </c>
+      <c r="D37" t="s">
+        <v>162</v>
+      </c>
+      <c r="E37" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>22330051920081</v>
+      </c>
+      <c r="B38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38" t="s">
+        <v>64</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>22330051920079</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" t="s">
+        <v>77</v>
+      </c>
+      <c r="D39" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>22330051920080</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" t="s">
+        <v>101</v>
+      </c>
+      <c r="D40" t="s">
+        <v>165</v>
+      </c>
+      <c r="E40" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>22330051920082</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>22330051920083</v>
+      </c>
+      <c r="B42" t="s">
+        <v>100</v>
+      </c>
+      <c r="C42" t="s">
+        <v>78</v>
+      </c>
+      <c r="D42" t="s">
+        <v>167</v>
+      </c>
+      <c r="E42" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="169">
   <si>
     <t>Materia</t>
   </si>
@@ -1014,7 +1014,7 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>7</v>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1091,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>5</v>
@@ -1145,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -1168,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -1222,7 +1222,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1245,7 +1245,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
         <v>6</v>
@@ -1299,7 +1299,7 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1322,7 +1322,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>9</v>
@@ -1376,7 +1376,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1399,7 +1399,7 @@
         <v>10</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D9">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>7</v>
@@ -1530,7 +1530,7 @@
         <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1607,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1630,7 +1630,7 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1684,7 +1684,7 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -1707,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>9</v>
@@ -1761,7 +1761,7 @@
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>9</v>
@@ -1784,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>6</v>
@@ -1838,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1861,7 +1861,7 @@
         <v>9</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D15">
         <v>7</v>
@@ -1915,7 +1915,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>7</v>
@@ -1938,7 +1938,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1992,7 +1992,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2015,7 +2015,7 @@
         <v>6</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -2069,7 +2069,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2092,7 +2092,7 @@
         <v>8</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -2146,7 +2146,7 @@
         <v>8</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2169,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -2223,7 +2223,7 @@
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2246,7 +2246,7 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2300,7 +2300,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2323,7 +2323,7 @@
         <v>9</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D21">
         <v>8</v>
@@ -2377,7 +2377,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2400,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>6</v>
@@ -2454,7 +2454,7 @@
         <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2477,7 +2477,7 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D23">
         <v>6</v>
@@ -2531,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>6</v>
@@ -2554,7 +2554,7 @@
         <v>10</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D24">
         <v>8</v>
@@ -2608,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2685,7 +2685,7 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>6</v>
@@ -2708,7 +2708,7 @@
         <v>8</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D26">
         <v>8</v>
@@ -2762,7 +2762,7 @@
         <v>8</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2785,7 +2785,7 @@
         <v>6</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>9</v>
@@ -2839,7 +2839,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2862,7 +2862,7 @@
         <v>5</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -2916,7 +2916,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2939,7 +2939,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -2993,7 +2993,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3016,7 +3016,7 @@
         <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -3070,7 +3070,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>6</v>
@@ -3093,7 +3093,7 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>7</v>
@@ -3147,7 +3147,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -3170,7 +3170,7 @@
         <v>5</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>5</v>
@@ -3224,7 +3224,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3247,7 +3247,7 @@
         <v>10</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D33">
         <v>8</v>
@@ -3301,7 +3301,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3324,7 +3324,7 @@
         <v>10</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -3378,7 +3378,7 @@
         <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3401,7 +3401,7 @@
         <v>8</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
         <v>8</v>
@@ -3455,7 +3455,7 @@
         <v>8</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3478,7 +3478,7 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D36">
         <v>9</v>
@@ -3532,7 +3532,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3555,7 +3555,7 @@
         <v>9</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D37">
         <v>8</v>
@@ -3609,7 +3609,7 @@
         <v>9</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3632,7 +3632,7 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>8</v>
@@ -3686,7 +3686,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3709,7 +3709,7 @@
         <v>10</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D39">
         <v>8</v>
@@ -3763,7 +3763,7 @@
         <v>10</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
         <v>8</v>
@@ -3786,7 +3786,7 @@
         <v>8</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>7</v>
@@ -3840,7 +3840,7 @@
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3863,7 +3863,7 @@
         <v>10</v>
       </c>
       <c r="C41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D41">
         <v>8</v>
@@ -3917,7 +3917,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3940,7 +3940,7 @@
         <v>10</v>
       </c>
       <c r="C42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D42">
         <v>7</v>
@@ -3994,7 +3994,7 @@
         <v>10</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -4017,7 +4017,7 @@
         <v>7</v>
       </c>
       <c r="C43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D43">
         <v>6</v>
@@ -4071,7 +4071,7 @@
         <v>7</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V43">
         <v>6</v>
@@ -4204,7 +4204,7 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>120</v>
@@ -4263,7 +4263,7 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
         <v>115</v>
@@ -4322,7 +4322,7 @@
         <v>100</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D6">
         <v>115</v>
@@ -4381,7 +4381,7 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>120</v>
@@ -4440,7 +4440,7 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>110</v>
@@ -4499,7 +4499,7 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>120</v>
@@ -4558,7 +4558,7 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
@@ -4617,7 +4617,7 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>120</v>
@@ -4676,7 +4676,7 @@
         <v>100</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>120</v>
@@ -4735,7 +4735,7 @@
         <v>100</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>115</v>
@@ -4794,7 +4794,7 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
         <v>115</v>
@@ -4853,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>120</v>
@@ -4912,7 +4912,7 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>120</v>
@@ -4971,7 +4971,7 @@
         <v>100</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
         <v>100</v>
@@ -5030,7 +5030,7 @@
         <v>100</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>115</v>
@@ -5148,7 +5148,7 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>120</v>
@@ -5207,7 +5207,7 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>110</v>
@@ -5266,7 +5266,7 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>110</v>
@@ -5325,7 +5325,7 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
         <v>100</v>
@@ -5384,7 +5384,7 @@
         <v>100</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
         <v>120</v>
@@ -5443,7 +5443,7 @@
         <v>100</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>115</v>
@@ -5502,7 +5502,7 @@
         <v>100</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D26">
         <v>120</v>
@@ -5561,7 +5561,7 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D27">
         <v>120</v>
@@ -5620,7 +5620,7 @@
         <v>90</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D28">
         <v>100</v>
@@ -5679,7 +5679,7 @@
         <v>100</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
         <v>120</v>
@@ -5738,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>120</v>
@@ -5797,7 +5797,7 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
         <v>110</v>
@@ -5856,7 +5856,7 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>28.6</v>
       </c>
       <c r="D32">
         <v>30</v>
@@ -5915,7 +5915,7 @@
         <v>100</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D33">
         <v>120</v>
@@ -5974,7 +5974,7 @@
         <v>100</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
         <v>120</v>
@@ -6033,7 +6033,7 @@
         <v>100</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
         <v>105</v>
@@ -6092,7 +6092,7 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
         <v>120</v>
@@ -6151,7 +6151,7 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
         <v>120</v>
@@ -6210,7 +6210,7 @@
         <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
         <v>100</v>
@@ -6269,7 +6269,7 @@
         <v>100</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D39">
         <v>120</v>
@@ -6328,7 +6328,7 @@
         <v>100</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
         <v>120</v>
@@ -6387,7 +6387,7 @@
         <v>100</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D41">
         <v>115</v>
@@ -6446,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D42">
         <v>115</v>
@@ -6505,7 +6505,7 @@
         <v>100</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D43">
         <v>120</v>
@@ -6608,7 +6608,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -6617,27 +6617,30 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>15</v>
+      </c>
+      <c r="H2">
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6646,19 +6649,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6669,7 +6672,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>64</v>
@@ -6690,7 +6693,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6701,7 +6704,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6710,19 +6713,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>87.5</v>
+        <v>92.5</v>
       </c>
       <c r="G5">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6733,7 +6736,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6742,19 +6745,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="G6">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6765,7 +6768,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -6786,7 +6789,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6802,7 +6805,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6827,806 +6830,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920052</v>
-      </c>
-      <c r="B2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920333</v>
-      </c>
-      <c r="B3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920053</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920054</v>
-      </c>
-      <c r="B5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920055</v>
-      </c>
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920208</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" t="s">
-        <v>134</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920057</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920058</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>106</v>
-      </c>
-      <c r="D9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920059</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>137</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920061</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920062</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D12" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920060</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920063</v>
-      </c>
-      <c r="B14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D14" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920212</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>112</v>
-      </c>
-      <c r="D15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920064</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>113</v>
-      </c>
-      <c r="D16" t="s">
-        <v>143</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920065</v>
-      </c>
-      <c r="B17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920066</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D18" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920316</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" t="s">
-        <v>146</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920334</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22230030070114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>117</v>
-      </c>
-      <c r="D21" t="s">
-        <v>148</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920067</v>
-      </c>
-      <c r="B22" t="s">
-        <v>85</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920335</v>
-      </c>
-      <c r="B23" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>119</v>
-      </c>
-      <c r="D23" t="s">
-        <v>150</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920380</v>
-      </c>
-      <c r="B24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" t="s">
-        <v>151</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920068</v>
-      </c>
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
-      </c>
-      <c r="D25" t="s">
-        <v>152</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920069</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>121</v>
-      </c>
-      <c r="D26" t="s">
-        <v>153</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920070</v>
-      </c>
-      <c r="B27" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>154</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920071</v>
-      </c>
-      <c r="B28" t="s">
-        <v>90</v>
-      </c>
-      <c r="C28" t="s">
-        <v>123</v>
-      </c>
-      <c r="D28" t="s">
-        <v>155</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920317</v>
-      </c>
-      <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" t="s">
-        <v>156</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920072</v>
-      </c>
-      <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>124</v>
-      </c>
-      <c r="D30" t="s">
-        <v>157</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920073</v>
-      </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" t="s">
-        <v>114</v>
-      </c>
-      <c r="D31" t="s">
-        <v>158</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920075</v>
-      </c>
-      <c r="B32" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920076</v>
-      </c>
-      <c r="B33" t="s">
-        <v>94</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920077</v>
-      </c>
-      <c r="B34" t="s">
-        <v>95</v>
-      </c>
-      <c r="C34" t="s">
-        <v>97</v>
-      </c>
-      <c r="D34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920078</v>
-      </c>
-      <c r="B35" t="s">
-        <v>96</v>
-      </c>
-      <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" t="s">
-        <v>162</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920081</v>
-      </c>
-      <c r="B36" t="s">
-        <v>97</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" t="s">
-        <v>163</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920079</v>
-      </c>
-      <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" t="s">
-        <v>77</v>
-      </c>
-      <c r="D37" t="s">
-        <v>164</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920080</v>
-      </c>
-      <c r="B38" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" t="s">
-        <v>165</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920082</v>
-      </c>
-      <c r="B39" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" t="s">
-        <v>128</v>
-      </c>
-      <c r="D39" t="s">
-        <v>166</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920083</v>
-      </c>
-      <c r="B40" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" t="s">
-        <v>78</v>
-      </c>
-      <c r="D40" t="s">
-        <v>167</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920084</v>
-      </c>
-      <c r="B41" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" t="s">
-        <v>115</v>
-      </c>
-      <c r="D41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -7674,7 +6877,7 @@
         <v>129</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7691,7 +6894,7 @@
         <v>130</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7708,7 +6911,7 @@
         <v>131</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7725,7 +6928,7 @@
         <v>132</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7742,7 +6945,7 @@
         <v>133</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7759,7 +6962,7 @@
         <v>134</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -7776,7 +6979,7 @@
         <v>135</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -7793,7 +6996,7 @@
         <v>136</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -7810,7 +7013,7 @@
         <v>137</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -7827,7 +7030,7 @@
         <v>138</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -7844,7 +7047,7 @@
         <v>139</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -7861,7 +7064,7 @@
         <v>140</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -7878,7 +7081,7 @@
         <v>141</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -7895,7 +7098,7 @@
         <v>142</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -7912,7 +7115,7 @@
         <v>143</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -7929,7 +7132,7 @@
         <v>144</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -7946,7 +7149,7 @@
         <v>145</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -7963,7 +7166,7 @@
         <v>146</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -7980,7 +7183,7 @@
         <v>147</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -7997,7 +7200,7 @@
         <v>148</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8014,7 +7217,7 @@
         <v>149</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8031,7 +7234,7 @@
         <v>150</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8048,7 +7251,7 @@
         <v>151</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8065,7 +7268,7 @@
         <v>152</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8082,7 +7285,7 @@
         <v>153</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8099,7 +7302,7 @@
         <v>154</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8116,7 +7319,7 @@
         <v>155</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8133,7 +7336,7 @@
         <v>156</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8150,7 +7353,7 @@
         <v>157</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8167,7 +7370,7 @@
         <v>158</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8184,7 +7387,7 @@
         <v>159</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8201,7 +7404,7 @@
         <v>160</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8218,7 +7421,7 @@
         <v>161</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8235,7 +7438,7 @@
         <v>162</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8252,7 +7455,7 @@
         <v>163</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8269,7 +7472,7 @@
         <v>164</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8286,7 +7489,7 @@
         <v>165</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -8303,7 +7506,7 @@
         <v>166</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -8320,7 +7523,7 @@
         <v>167</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -8337,7 +7540,7 @@
         <v>168</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8347,7 +7550,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8379,42 +7582,42 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920333</v>
+        <v>22330051920084</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>64</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920333</v>
+        <v>22330051920084</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>64</v>
@@ -8425,25 +7628,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920212</v>
+        <v>22330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8483,30 +7686,30 @@
         <v>152</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>22330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>64</v>
@@ -8517,807 +7720,25 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920070</v>
+        <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>
       </c>
       <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920070</v>
-      </c>
-      <c r="B9" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" t="s">
-        <v>122</v>
-      </c>
-      <c r="D9" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G9">
         <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920071</v>
-      </c>
-      <c r="B10" t="s">
-        <v>90</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-      <c r="D10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920071</v>
-      </c>
-      <c r="B11" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" t="s">
-        <v>155</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>64</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920052</v>
-      </c>
-      <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>64</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920053</v>
-      </c>
-      <c r="B13" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" t="s">
-        <v>131</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920054</v>
-      </c>
-      <c r="B14" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920055</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920208</v>
-      </c>
-      <c r="B16" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920057</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>64</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920058</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920059</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" t="s">
-        <v>137</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920061</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>138</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920062</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>64</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920060</v>
-      </c>
-      <c r="B22" t="s">
-        <v>79</v>
-      </c>
-      <c r="C22" t="s">
-        <v>110</v>
-      </c>
-      <c r="D22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>64</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920063</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920064</v>
-      </c>
-      <c r="B24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>64</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920066</v>
-      </c>
-      <c r="B25" t="s">
-        <v>81</v>
-      </c>
-      <c r="C25" t="s">
-        <v>115</v>
-      </c>
-      <c r="D25" t="s">
-        <v>145</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920316</v>
-      </c>
-      <c r="B26" t="s">
-        <v>82</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920334</v>
-      </c>
-      <c r="B27" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>64</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22230030070114</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>117</v>
-      </c>
-      <c r="D28" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>64</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920067</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920335</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>64</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920380</v>
-      </c>
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>120</v>
-      </c>
-      <c r="D31" t="s">
-        <v>151</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920317</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>156</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>64</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920073</v>
-      </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>64</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920075</v>
-      </c>
-      <c r="B34" t="s">
-        <v>94</v>
-      </c>
-      <c r="C34" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>64</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920076</v>
-      </c>
-      <c r="B35" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D35" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920077</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
-      </c>
-      <c r="C36" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" t="s">
-        <v>161</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>64</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920078</v>
-      </c>
-      <c r="B37" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D37" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>64</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920081</v>
-      </c>
-      <c r="B38" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" t="s">
-        <v>127</v>
-      </c>
-      <c r="D38" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>64</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920079</v>
-      </c>
-      <c r="B39" t="s">
-        <v>96</v>
-      </c>
-      <c r="C39" t="s">
-        <v>77</v>
-      </c>
-      <c r="D39" t="s">
-        <v>164</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>64</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920080</v>
-      </c>
-      <c r="B40" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D40" t="s">
-        <v>165</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>64</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920082</v>
-      </c>
-      <c r="B41" t="s">
-        <v>99</v>
-      </c>
-      <c r="C41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D41" t="s">
-        <v>166</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>64</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>22330051920083</v>
-      </c>
-      <c r="B42" t="s">
-        <v>100</v>
-      </c>
-      <c r="C42" t="s">
-        <v>78</v>
-      </c>
-      <c r="D42" t="s">
-        <v>167</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>64</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="174">
   <si>
     <t>Materia</t>
   </si>
@@ -213,7 +213,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
   </si>
   <si>
     <t>NC</t>
@@ -6643,7 +6658,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3">
         <v>40</v>
@@ -6675,7 +6690,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -6707,7 +6722,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -6739,7 +6754,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C6">
         <v>40</v>
@@ -6771,7 +6786,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -6814,16 +6829,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6848,16 +6863,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>62</v>
@@ -6868,13 +6883,13 @@
         <v>22330051920052</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6885,13 +6900,13 @@
         <v>22330051920333</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6902,13 +6917,13 @@
         <v>22330051920053</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6919,13 +6934,13 @@
         <v>22330051920054</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6936,13 +6951,13 @@
         <v>22330051920055</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6953,13 +6968,13 @@
         <v>22330051920208</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6970,13 +6985,13 @@
         <v>22330051920057</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6987,13 +7002,13 @@
         <v>22330051920058</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -7004,13 +7019,13 @@
         <v>22330051920059</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -7021,13 +7036,13 @@
         <v>22330051920061</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -7038,13 +7053,13 @@
         <v>22330051920062</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -7055,13 +7070,13 @@
         <v>22330051920060</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -7072,13 +7087,13 @@
         <v>22330051920063</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -7089,13 +7104,13 @@
         <v>22330051920212</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -7106,13 +7121,13 @@
         <v>22330051920064</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -7123,13 +7138,13 @@
         <v>22330051920065</v>
       </c>
       <c r="B17" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -7140,13 +7155,13 @@
         <v>22330051920066</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -7157,13 +7172,13 @@
         <v>22330051920316</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -7174,13 +7189,13 @@
         <v>22330051920334</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -7191,13 +7206,13 @@
         <v>22230030070114</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -7208,13 +7223,13 @@
         <v>22330051920067</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -7225,13 +7240,13 @@
         <v>22330051920335</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -7242,13 +7257,13 @@
         <v>22330051920380</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -7259,13 +7274,13 @@
         <v>22330051920068</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -7276,13 +7291,13 @@
         <v>22330051920069</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -7293,13 +7308,13 @@
         <v>22330051920070</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -7310,13 +7325,13 @@
         <v>22330051920071</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -7327,13 +7342,13 @@
         <v>22330051920317</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -7344,13 +7359,13 @@
         <v>22330051920072</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -7361,13 +7376,13 @@
         <v>22330051920073</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -7378,13 +7393,13 @@
         <v>22330051920075</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -7395,13 +7410,13 @@
         <v>22330051920076</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -7412,13 +7427,13 @@
         <v>22330051920077</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7429,13 +7444,13 @@
         <v>22330051920078</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7446,13 +7461,13 @@
         <v>22330051920081</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D36" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7463,13 +7478,13 @@
         <v>22330051920079</v>
       </c>
       <c r="B37" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7480,13 +7495,13 @@
         <v>22330051920080</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7497,13 +7512,13 @@
         <v>22330051920082</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -7514,13 +7529,13 @@
         <v>22330051920083</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -7531,13 +7546,13 @@
         <v>22330051920084</v>
       </c>
       <c r="B41" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C41" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -7559,16 +7574,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7585,13 +7600,13 @@
         <v>22330051920084</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D2" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -7608,19 +7623,19 @@
         <v>22330051920084</v>
       </c>
       <c r="B3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7631,19 +7646,19 @@
         <v>22330051920333</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7654,19 +7669,19 @@
         <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7677,13 +7692,13 @@
         <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7700,19 +7715,19 @@
         <v>22330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7723,13 +7738,13 @@
         <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -243,63 +242,15 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ABAD</t>
+    <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>AYOHUA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CAHUICH</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>MACHORRO</t>
   </si>
   <si>
@@ -309,244 +260,49 @@
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
-    <t>PUGA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RICO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TERRAZAS</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>DORANTES</t>
+    <t>TEXCAHUA</t>
   </si>
   <si>
     <t>COXCAHUA</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CHIMALHUA</t>
-  </si>
-  <si>
-    <t>ESPEJO</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>MORA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>SILVA</t>
-  </si>
-  <si>
-    <t>VELASQUEZ</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>CARRASCO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>CITLALLI</t>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>FRANCISCO JAVIER</t>
   </si>
   <si>
-    <t>LUIS FELIPE</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>MARIA CHRISTINA</t>
-  </si>
-  <si>
-    <t>MELANY SHARENY</t>
-  </si>
-  <si>
-    <t>NATALIA</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>SALMA AISHA</t>
-  </si>
-  <si>
-    <t>LESLIE PAOLA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>DANIEL ELEAZAR</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>ARANZA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA CECILIA</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>HANNY YUSETH</t>
-  </si>
-  <si>
-    <t>ESTRELLA</t>
-  </si>
-  <si>
-    <t>MARIA ELISA</t>
-  </si>
-  <si>
-    <t>CARLOS EDUARDO</t>
-  </si>
-  <si>
     <t>JIMENA</t>
   </si>
   <si>
-    <t>LUZ YAMILET</t>
-  </si>
-  <si>
     <t>ROSA</t>
   </si>
   <si>
     <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>JESUS ALEJANDRO</t>
-  </si>
-  <si>
-    <t>NICOLAS</t>
-  </si>
-  <si>
-    <t>HILEN ALELI</t>
-  </si>
-  <si>
-    <t>MIRANDA</t>
-  </si>
-  <si>
-    <t>ULISES</t>
-  </si>
-  <si>
-    <t>MAYRIN FERNANDA</t>
-  </si>
-  <si>
-    <t>ARLETT ALEJANDRA</t>
-  </si>
-  <si>
-    <t>ALEXANDRA</t>
-  </si>
-  <si>
-    <t>MELANIE SOFIA</t>
-  </si>
-  <si>
-    <t>DORIS ALINE</t>
-  </si>
-  <si>
-    <t>MAYDALITH</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -599,11 +355,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1044,7 +801,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1121,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1157,7 +914,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5">
         <v>7</v>
@@ -1198,7 +955,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1275,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1352,7 +1109,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1429,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1465,7 +1222,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1506,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1583,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1660,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1737,7 +1494,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1814,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1891,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1927,7 +1684,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1968,7 +1725,7 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2045,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2122,7 +1879,7 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2158,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2199,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2276,7 +2033,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2353,7 +2110,7 @@
         <v>8</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2430,7 +2187,7 @@
         <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2466,7 +2223,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2507,7 +2264,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2543,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2584,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2661,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2738,7 +2495,7 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2774,7 +2531,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2815,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2892,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2969,7 +2726,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3046,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3082,7 +2839,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3123,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3159,7 +2916,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U31">
         <v>8</v>
@@ -3200,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3277,7 +3034,7 @@
         <v>9</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3354,7 +3111,7 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3431,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3508,7 +3265,7 @@
         <v>9</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3585,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3621,7 +3378,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3662,7 +3419,7 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3739,7 +3496,7 @@
         <v>10</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3816,7 +3573,7 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3852,7 +3609,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U40">
         <v>8</v>
@@ -3893,7 +3650,7 @@
         <v>9</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -3970,7 +3727,7 @@
         <v>10</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -4006,7 +3763,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U42">
         <v>8</v>
@@ -4047,7 +3804,7 @@
         <v>5</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I43">
         <v>-1</v>
@@ -4234,7 +3991,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4293,7 +4050,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4352,7 +4109,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4411,7 +4168,7 @@
         <v>95</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4470,7 +4227,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4529,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4588,7 +4345,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4647,7 +4404,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4706,7 +4463,7 @@
         <v>95</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4765,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4824,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4883,7 +4640,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4942,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -5001,7 +4758,7 @@
         <v>100</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -5060,7 +4817,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -5178,7 +4935,7 @@
         <v>95</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -5237,7 +4994,7 @@
         <v>95</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5296,7 +5053,7 @@
         <v>100</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5355,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5414,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5473,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5532,7 +5289,7 @@
         <v>100</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5591,7 +5348,7 @@
         <v>95</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5650,7 +5407,7 @@
         <v>50</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5709,7 +5466,7 @@
         <v>90</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5768,7 +5525,7 @@
         <v>95</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5827,7 +5584,7 @@
         <v>95</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5945,7 +5702,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -6004,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -6063,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -6122,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -6181,7 +5938,7 @@
         <v>100</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -6240,7 +5997,7 @@
         <v>100</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6299,7 +6056,7 @@
         <v>100</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -6358,7 +6115,7 @@
         <v>95</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6417,7 +6174,7 @@
         <v>100</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -6476,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="H42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -6535,7 +6292,7 @@
         <v>85</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -6587,6 +6344,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6637,10 +6396,10 @@
       <c r="E2">
         <v>6</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>85</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>15</v>
       </c>
       <c r="H2">
@@ -6649,7 +6408,7 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6669,10 +6428,10 @@
       <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>87.5</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>12.5</v>
       </c>
       <c r="H3">
@@ -6681,7 +6440,7 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6701,10 +6460,10 @@
       <c r="E4">
         <v>5</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>87.5</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>12.5</v>
       </c>
       <c r="H4">
@@ -6713,7 +6472,7 @@
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6733,19 +6492,19 @@
       <c r="E5">
         <v>3</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>92.5</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>7.5</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6765,10 +6524,10 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>95</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>5</v>
       </c>
       <c r="H6">
@@ -6777,7 +6536,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6797,10 +6556,10 @@
       <c r="E7">
         <v>2</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>95</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>5</v>
       </c>
       <c r="H7">
@@ -6809,7 +6568,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6854,717 +6613,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920052</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920333</v>
-      </c>
-      <c r="B3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920053</v>
-      </c>
-      <c r="B4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920054</v>
-      </c>
-      <c r="B5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920055</v>
-      </c>
-      <c r="B6" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920208</v>
-      </c>
-      <c r="B7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920057</v>
-      </c>
-      <c r="B8" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" t="s">
-        <v>83</v>
-      </c>
-      <c r="D8" t="s">
-        <v>140</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920058</v>
-      </c>
-      <c r="B9" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" t="s">
-        <v>111</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920059</v>
-      </c>
-      <c r="B10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D10" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920061</v>
-      </c>
-      <c r="B11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920062</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920060</v>
-      </c>
-      <c r="B13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920063</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D14" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920212</v>
-      </c>
-      <c r="B15" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" t="s">
-        <v>147</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920064</v>
-      </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920065</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920066</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
-      </c>
-      <c r="C18" t="s">
-        <v>120</v>
-      </c>
-      <c r="D18" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920316</v>
-      </c>
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>121</v>
-      </c>
-      <c r="D19" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920334</v>
-      </c>
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
-      </c>
-      <c r="D20" t="s">
-        <v>152</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22230030070114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C21" t="s">
-        <v>122</v>
-      </c>
-      <c r="D21" t="s">
-        <v>153</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920067</v>
-      </c>
-      <c r="B22" t="s">
-        <v>90</v>
-      </c>
-      <c r="C22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920335</v>
-      </c>
-      <c r="B23" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" t="s">
-        <v>155</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920380</v>
-      </c>
-      <c r="B24" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920068</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" t="s">
-        <v>157</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920069</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920070</v>
-      </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" t="s">
-        <v>127</v>
-      </c>
-      <c r="D27" t="s">
-        <v>159</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920071</v>
-      </c>
-      <c r="B28" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D28" t="s">
-        <v>160</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920317</v>
-      </c>
-      <c r="B29" t="s">
-        <v>96</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s">
-        <v>161</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920072</v>
-      </c>
-      <c r="B30" t="s">
-        <v>97</v>
-      </c>
-      <c r="C30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D30" t="s">
-        <v>162</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920073</v>
-      </c>
-      <c r="B31" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" t="s">
-        <v>119</v>
-      </c>
-      <c r="D31" t="s">
-        <v>163</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920075</v>
-      </c>
-      <c r="B32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C32" t="s">
-        <v>130</v>
-      </c>
-      <c r="D32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920076</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>104</v>
-      </c>
-      <c r="D33" t="s">
-        <v>165</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920077</v>
-      </c>
-      <c r="B34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>166</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920078</v>
-      </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D35" t="s">
-        <v>167</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920081</v>
-      </c>
-      <c r="B36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C36" t="s">
-        <v>132</v>
-      </c>
-      <c r="D36" t="s">
-        <v>168</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920079</v>
-      </c>
-      <c r="B37" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D37" t="s">
-        <v>169</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920080</v>
-      </c>
-      <c r="B38" t="s">
-        <v>103</v>
-      </c>
-      <c r="C38" t="s">
-        <v>106</v>
-      </c>
-      <c r="D38" t="s">
-        <v>170</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
-        <v>22330051920082</v>
-      </c>
-      <c r="B39" t="s">
-        <v>104</v>
-      </c>
-      <c r="C39" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
-        <v>22330051920083</v>
-      </c>
-      <c r="B40" t="s">
-        <v>105</v>
-      </c>
-      <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>172</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
-        <v>22330051920084</v>
-      </c>
-      <c r="B41" t="s">
-        <v>106</v>
-      </c>
-      <c r="C41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" t="s">
-        <v>173</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -7600,13 +6648,13 @@
         <v>22330051920084</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -7623,13 +6671,13 @@
         <v>22330051920084</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>173</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -7649,10 +6697,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -7669,13 +6717,13 @@
         <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -7692,13 +6740,13 @@
         <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -7715,13 +6763,13 @@
         <v>22330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -7738,13 +6786,13 @@
         <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
   <si>
     <t>Materia</t>
   </si>
@@ -212,10 +212,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>Rodríguez Román Leticia</t>
@@ -224,9 +227,6 @@
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Castro Vasquez Julieta</t>
   </si>
   <si>
@@ -242,15 +242,12 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>AYOHUA</t>
-  </si>
-  <si>
     <t>GUERRA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
@@ -260,15 +257,15 @@
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
+    <t>ORTEGA</t>
   </si>
   <si>
     <t>RIVERA</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -278,15 +275,12 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>FRANCISCO JAVIER</t>
-  </si>
-  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
+    <t>DANIELA</t>
+  </si>
+  <si>
     <t>JIMENA</t>
   </si>
   <si>
@@ -294,6 +288,9 @@
   </si>
   <si>
     <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>JESUS ALEJANDRO</t>
   </si>
 </sst>
 </file>
@@ -810,13 +807,13 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -846,13 +843,13 @@
         <v>7</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -887,13 +884,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -923,10 +920,10 @@
         <v>5</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -964,13 +961,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1003,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1041,13 +1038,13 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1080,10 +1077,10 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1118,13 +1115,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1195,13 +1192,13 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1237,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1272,13 +1269,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1308,13 +1305,13 @@
         <v>7</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1349,13 +1346,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1426,13 +1423,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1465,7 +1462,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1503,13 +1500,13 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1545,7 +1542,7 @@
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1580,13 +1577,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1619,10 +1616,10 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1657,13 +1654,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1696,10 +1693,10 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1734,13 +1731,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1770,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1811,13 +1808,13 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1850,10 +1847,10 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1888,13 +1885,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1924,13 +1921,13 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1965,13 +1962,13 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2042,13 +2039,13 @@
         <v>-1</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2119,13 +2116,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2155,13 +2152,13 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2196,13 +2193,13 @@
         <v>-1</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2273,13 +2270,13 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2312,10 +2309,10 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2350,13 +2347,13 @@
         <v>-1</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2386,13 +2383,13 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2427,13 +2424,13 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2469,7 +2466,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2504,13 +2501,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2581,13 +2578,13 @@
         <v>-1</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2620,10 +2617,10 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2658,13 +2655,13 @@
         <v>-1</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2694,7 +2691,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2735,13 +2732,13 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2771,7 +2768,7 @@
         <v>7</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2812,13 +2809,13 @@
         <v>-1</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2848,13 +2845,13 @@
         <v>6</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2889,13 +2886,13 @@
         <v>-1</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2925,13 +2922,13 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X31">
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2966,13 +2963,13 @@
         <v>-1</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3043,13 +3040,13 @@
         <v>-1</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3085,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3120,13 +3117,13 @@
         <v>-1</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3197,13 +3194,13 @@
         <v>-1</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3274,13 +3271,13 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3351,13 +3348,13 @@
         <v>-1</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3387,7 +3384,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3428,13 +3425,13 @@
         <v>-1</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3467,10 +3464,10 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y38">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3505,13 +3502,13 @@
         <v>-1</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3582,13 +3579,13 @@
         <v>-1</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3659,13 +3656,13 @@
         <v>-1</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3701,7 +3698,7 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3736,13 +3733,13 @@
         <v>-1</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -3772,13 +3769,13 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X42">
         <v>10</v>
       </c>
       <c r="Y42">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3813,13 +3810,13 @@
         <v>-1</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -3849,7 +3846,7 @@
         <v>6</v>
       </c>
       <c r="W43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X43">
         <v>5</v>
@@ -4000,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4059,13 +4056,13 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4118,13 +4115,13 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4177,13 +4174,13 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4236,13 +4233,13 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4295,13 +4292,13 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4354,13 +4351,13 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4413,13 +4410,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4472,13 +4469,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4531,13 +4528,13 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4590,13 +4587,13 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4649,13 +4646,13 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4708,13 +4705,13 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4767,13 +4764,13 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4826,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4944,13 +4941,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -5003,13 +5000,13 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5062,13 +5059,13 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5121,13 +5118,13 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5180,13 +5177,13 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5239,13 +5236,13 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5298,13 +5295,13 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5357,13 +5354,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5416,13 +5413,13 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5475,13 +5472,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5534,13 +5531,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5593,13 +5590,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5711,13 +5708,13 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5770,13 +5767,13 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5829,13 +5826,13 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5888,13 +5885,13 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5947,13 +5944,13 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -6006,13 +6003,13 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6065,13 +6062,13 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6124,13 +6121,13 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6183,13 +6180,13 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N41">
         <v>0</v>
@@ -6242,13 +6239,13 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -6301,13 +6298,13 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M43">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -6382,7 +6379,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -6391,19 +6388,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G2" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6414,7 +6411,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6423,19 +6420,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>87.5</v>
+        <v>82.5</v>
       </c>
       <c r="G3" s="2">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6446,7 +6443,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -6467,7 +6464,7 @@
         <v>12.5</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6478,7 +6475,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -6487,19 +6484,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>92.5</v>
+        <v>87.5</v>
       </c>
       <c r="G5" s="2">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6510,7 +6507,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>68</v>
@@ -6519,19 +6516,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="G6" s="2">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6645,7 +6642,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920084</v>
+        <v>22330051920212</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
@@ -6654,13 +6651,13 @@
         <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6668,7 +6665,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920084</v>
+        <v>22330051920212</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
@@ -6677,13 +6674,13 @@
         <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6691,7 +6688,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920333</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
@@ -6700,13 +6697,13 @@
         <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6714,7 +6711,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920068</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
@@ -6723,13 +6720,13 @@
         <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6737,7 +6734,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920068</v>
+        <v>22330051920070</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
@@ -6746,10 +6743,10 @@
         <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -6760,7 +6757,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920070</v>
+        <v>22330051920071</v>
       </c>
       <c r="B7" t="s">
         <v>78</v>
@@ -6769,10 +6766,10 @@
         <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
@@ -6783,19 +6780,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920071</v>
+        <v>22330051920317</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -801,7 +801,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>-1</v>
@@ -878,7 +878,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
         <v>-1</v>
@@ -914,7 +914,7 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -955,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
         <v>-1</v>
@@ -991,7 +991,7 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -1032,7 +1032,7 @@
         <v>6</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1109,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1145,7 +1145,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1186,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1263,7 +1263,7 @@
         <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1340,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
         <v>-1</v>
@@ -1417,7 +1417,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
         <v>-1</v>
@@ -1494,7 +1494,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1571,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1607,7 +1607,7 @@
         <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1648,7 +1648,7 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>-1</v>
@@ -1725,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -1802,7 +1802,7 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
         <v>-1</v>
@@ -1838,7 +1838,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1879,7 +1879,7 @@
         <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>-1</v>
@@ -1956,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2033,7 +2033,7 @@
         <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
         <v>-1</v>
@@ -2069,7 +2069,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2110,7 +2110,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2146,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2187,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
         <v>-1</v>
@@ -2264,7 +2264,7 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2341,7 +2341,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>-1</v>
@@ -2377,7 +2377,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2418,7 +2418,7 @@
         <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2495,7 +2495,7 @@
         <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2572,7 +2572,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>-1</v>
@@ -2608,7 +2608,7 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>9</v>
@@ -2649,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>-1</v>
@@ -2685,7 +2685,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2726,7 +2726,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -2803,7 +2803,7 @@
         <v>6</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
         <v>-1</v>
@@ -2880,7 +2880,7 @@
         <v>6</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>-1</v>
@@ -2916,7 +2916,7 @@
         <v>7</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>7</v>
@@ -2957,7 +2957,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>-1</v>
@@ -3034,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
         <v>-1</v>
@@ -3111,7 +3111,7 @@
         <v>10</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
         <v>-1</v>
@@ -3188,7 +3188,7 @@
         <v>8</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
         <v>-1</v>
@@ -3265,7 +3265,7 @@
         <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3301,7 +3301,7 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3342,7 +3342,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
         <v>-1</v>
@@ -3378,7 +3378,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3419,7 +3419,7 @@
         <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
         <v>-1</v>
@@ -3455,7 +3455,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3496,7 +3496,7 @@
         <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J39">
         <v>-1</v>
@@ -3573,7 +3573,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
         <v>-1</v>
@@ -3609,7 +3609,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3650,7 +3650,7 @@
         <v>9</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>-1</v>
@@ -3686,7 +3686,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3727,7 +3727,7 @@
         <v>8</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J42">
         <v>-1</v>
@@ -3763,7 +3763,7 @@
         <v>9</v>
       </c>
       <c r="U42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V42">
         <v>7</v>
@@ -3804,7 +3804,7 @@
         <v>6</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J43">
         <v>-1</v>
@@ -3991,7 +3991,7 @@
         <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -4050,7 +4050,7 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -4109,7 +4109,7 @@
         <v>100</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -4286,7 +4286,7 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -4404,7 +4404,7 @@
         <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -4463,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -4522,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -4581,7 +4581,7 @@
         <v>100</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -4640,7 +4640,7 @@
         <v>100</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -4699,7 +4699,7 @@
         <v>100</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -4758,7 +4758,7 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -4817,7 +4817,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -4935,7 +4935,7 @@
         <v>100</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -5171,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J24">
         <v>0</v>
@@ -5230,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         <v>100</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -5407,7 +5407,7 @@
         <v>96</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -5466,7 +5466,7 @@
         <v>100</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>100</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -5584,7 +5584,7 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -5702,7 +5702,7 @@
         <v>100</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
         <v>0</v>
@@ -5761,7 +5761,7 @@
         <v>100</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
         <v>0</v>
@@ -5820,7 +5820,7 @@
         <v>100</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>94.3</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -5938,7 +5938,7 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>100</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>100</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>100</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -6233,7 +6233,7 @@
         <v>100</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J42">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>100</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J43">
         <v>0</v>
@@ -6560,7 +6560,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
   <si>
     <t>Materia</t>
   </si>
@@ -212,6 +212,9 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
@@ -221,9 +224,6 @@
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
@@ -242,52 +242,76 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JORGE</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>GUTIERREZ</t>
+    <t>DANIELA</t>
   </si>
   <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
     <t>JIMENA</t>
   </si>
   <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIEL ELEAZAR</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
     <t>ROSA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
   </si>
   <si>
     <t>JESUS ALEJANDRO</t>
@@ -804,7 +828,7 @@
         <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
         <v>7</v>
@@ -881,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>5</v>
@@ -958,7 +982,7 @@
         <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>6</v>
@@ -994,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1035,7 +1059,7 @@
         <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1071,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1112,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>10</v>
@@ -1189,7 +1213,7 @@
         <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K9">
         <v>8</v>
@@ -1225,7 +1249,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1266,7 +1290,7 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>10</v>
@@ -1343,7 +1367,7 @@
         <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -1379,7 +1403,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1420,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1497,7 +1521,7 @@
         <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>10</v>
@@ -1533,7 +1557,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>10</v>
@@ -1574,7 +1598,7 @@
         <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1610,7 +1634,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1651,7 +1675,7 @@
         <v>8</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K15">
         <v>9</v>
@@ -1687,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1728,7 +1752,7 @@
         <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>10</v>
@@ -1805,7 +1829,7 @@
         <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
         <v>7</v>
@@ -1882,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K18">
         <v>6</v>
@@ -1918,7 +1942,7 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1959,7 +1983,7 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -2036,7 +2060,7 @@
         <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
         <v>9</v>
@@ -2113,7 +2137,7 @@
         <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>6</v>
@@ -2149,7 +2173,7 @@
         <v>9</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2190,7 +2214,7 @@
         <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>6</v>
@@ -2226,7 +2250,7 @@
         <v>9</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2267,7 +2291,7 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
         <v>10</v>
@@ -2344,7 +2368,7 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
         <v>7</v>
@@ -2421,7 +2445,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
         <v>6</v>
@@ -2457,7 +2481,7 @@
         <v>7</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2498,7 +2522,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>9</v>
@@ -2534,7 +2558,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>10</v>
@@ -2575,7 +2599,7 @@
         <v>8</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>6</v>
@@ -2611,7 +2635,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2652,7 +2676,7 @@
         <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>5</v>
@@ -2729,7 +2753,7 @@
         <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>8</v>
@@ -2765,7 +2789,7 @@
         <v>9</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2806,7 +2830,7 @@
         <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>6</v>
@@ -2842,7 +2866,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>7</v>
@@ -2883,7 +2907,7 @@
         <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>6</v>
@@ -2919,7 +2943,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -2960,7 +2984,7 @@
         <v>5</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
         <v>5</v>
@@ -3037,7 +3061,7 @@
         <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
         <v>10</v>
@@ -3073,7 +3097,7 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3114,7 +3138,7 @@
         <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>10</v>
@@ -3191,7 +3215,7 @@
         <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K35">
         <v>8</v>
@@ -3227,7 +3251,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3268,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>10</v>
@@ -3345,7 +3369,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>10</v>
@@ -3422,7 +3446,7 @@
         <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K38">
         <v>7</v>
@@ -3458,7 +3482,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3499,7 +3523,7 @@
         <v>9</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>10</v>
@@ -3576,7 +3600,7 @@
         <v>9</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K40">
         <v>9</v>
@@ -3612,7 +3636,7 @@
         <v>9</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3653,7 +3677,7 @@
         <v>9</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>9</v>
@@ -3689,7 +3713,7 @@
         <v>9</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -3730,7 +3754,7 @@
         <v>9</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
         <v>8</v>
@@ -3807,7 +3831,7 @@
         <v>7</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K43">
         <v>5</v>
@@ -3843,7 +3867,7 @@
         <v>8</v>
       </c>
       <c r="V43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -3994,7 +4018,7 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K4">
         <v>86.7</v>
@@ -4053,7 +4077,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K5">
         <v>80</v>
@@ -4112,7 +4136,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -4171,7 +4195,7 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -4230,7 +4254,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -4289,7 +4313,7 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -4348,7 +4372,7 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -4407,7 +4431,7 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -4466,7 +4490,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -4525,7 +4549,7 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -4584,7 +4608,7 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -4643,7 +4667,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -4702,7 +4726,7 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -4761,7 +4785,7 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K17">
         <v>80</v>
@@ -4820,7 +4844,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4938,7 +4962,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K20">
         <v>80</v>
@@ -4997,7 +5021,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>86.7</v>
@@ -5056,7 +5080,7 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -5115,7 +5139,7 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -5174,7 +5198,7 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -5233,7 +5257,7 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -5292,7 +5316,7 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -5351,7 +5375,7 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -5410,7 +5434,7 @@
         <v>80</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="K28">
         <v>66.7</v>
@@ -5469,7 +5493,7 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -5528,7 +5552,7 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -5587,7 +5611,7 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -5705,7 +5729,7 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -5764,7 +5788,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5823,7 +5847,7 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -5882,7 +5906,7 @@
         <v>94.3</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -5941,7 +5965,7 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -6000,7 +6024,7 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -6059,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -6118,7 +6142,7 @@
         <v>100</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -6177,7 +6201,7 @@
         <v>100</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -6236,7 +6260,7 @@
         <v>100</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -6295,7 +6319,7 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -6379,7 +6403,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -6388,19 +6412,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6411,7 +6435,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6420,19 +6444,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="G3" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6443,7 +6467,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -6452,19 +6476,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>87.5</v>
+        <v>82.5</v>
       </c>
       <c r="G4" s="2">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6475,7 +6499,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>67</v>
@@ -6496,7 +6520,7 @@
         <v>12.5</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6610,7 +6634,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6642,22 +6666,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6665,22 +6689,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6688,19 +6712,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920061</v>
+        <v>22330051920212</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>64</v>
@@ -6711,19 +6735,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920068</v>
+        <v>22330051920212</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>65</v>
@@ -6734,19 +6758,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920070</v>
+        <v>22330051920068</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>64</v>
@@ -6757,22 +6781,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920071</v>
+        <v>22330051920068</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6780,24 +6804,162 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920317</v>
+        <v>22330051920071</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
         <v>64</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920071</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920054</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920064</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920334</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920070</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920317</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -4000,7 +4000,7 @@
         <v>100</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -4018,34 +4018,34 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K4">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L4">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="M4">
         <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -4059,7 +4059,7 @@
         <v>100</v>
       </c>
       <c r="D5">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4077,34 +4077,34 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L5">
-        <v>85</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="M5">
         <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4118,7 +4118,7 @@
         <v>100</v>
       </c>
       <c r="D6">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E6">
         <v>100</v>
@@ -4136,34 +4136,34 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>80</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K6">
         <v>100</v>
       </c>
       <c r="L6">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M6">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="D7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4201,28 +4201,28 @@
         <v>100</v>
       </c>
       <c r="L7">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M7">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4236,7 +4236,7 @@
         <v>100</v>
       </c>
       <c r="D8">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4254,34 +4254,34 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="K8">
         <v>100</v>
       </c>
       <c r="L8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4295,7 +4295,7 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
@@ -4313,34 +4313,34 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="K9">
         <v>100</v>
       </c>
       <c r="L9">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4354,7 +4354,7 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E10">
         <v>100</v>
@@ -4372,34 +4372,34 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M10">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4413,7 +4413,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4437,28 +4437,28 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4472,7 +4472,7 @@
         <v>100</v>
       </c>
       <c r="D12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>100</v>
@@ -4496,28 +4496,28 @@
         <v>100</v>
       </c>
       <c r="L12">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4531,7 +4531,7 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E13">
         <v>100</v>
@@ -4549,34 +4549,34 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="K13">
         <v>100</v>
       </c>
       <c r="L13">
-        <v>95</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4590,7 +4590,7 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4608,34 +4608,34 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>85</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K14">
         <v>100</v>
       </c>
       <c r="L14">
-        <v>105</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4649,7 +4649,7 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4667,34 +4667,34 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>83.3</v>
       </c>
       <c r="M15">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4708,7 +4708,7 @@
         <v>100</v>
       </c>
       <c r="D16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>100</v>
@@ -4732,28 +4732,28 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M16">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4767,7 +4767,7 @@
         <v>100</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E17">
         <v>100</v>
@@ -4785,34 +4785,34 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="K17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="M17">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>79.5</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4826,7 +4826,7 @@
         <v>100</v>
       </c>
       <c r="D18">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4844,34 +4844,34 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M18">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4944,7 +4944,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4962,34 +4962,34 @@
         <v>100</v>
       </c>
       <c r="J20">
+        <v>95.5</v>
+      </c>
+      <c r="K20">
         <v>90</v>
       </c>
-      <c r="K20">
-        <v>80</v>
-      </c>
       <c r="L20">
-        <v>105</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5003,7 +5003,7 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E21">
         <v>100</v>
@@ -5021,34 +5021,34 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="K21">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>93.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5062,7 +5062,7 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E22">
         <v>100</v>
@@ -5080,34 +5080,34 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K22">
         <v>100</v>
       </c>
       <c r="L22">
+        <v>85.7</v>
+      </c>
+      <c r="M22">
         <v>85</v>
       </c>
-      <c r="M22">
-        <v>70</v>
-      </c>
       <c r="N22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5121,7 +5121,7 @@
         <v>100</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5139,34 +5139,34 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K23">
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="M23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5180,7 +5180,7 @@
         <v>100</v>
       </c>
       <c r="D24">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -5204,28 +5204,28 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="M24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5239,7 +5239,7 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E25">
         <v>100</v>
@@ -5257,34 +5257,34 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>75</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K25">
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="M25">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5298,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="D26">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -5322,28 +5322,28 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5357,7 +5357,7 @@
         <v>100</v>
       </c>
       <c r="D27">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>86.7</v>
@@ -5375,34 +5375,34 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L27">
-        <v>85</v>
+        <v>76.2</v>
       </c>
       <c r="M27">
         <v>95</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5416,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="D28">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E28">
         <v>86.7</v>
@@ -5428,40 +5428,40 @@
         <v>50</v>
       </c>
       <c r="H28">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I28">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J28">
-        <v>45</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K28">
-        <v>66.7</v>
+        <v>76.7</v>
       </c>
       <c r="L28">
-        <v>5</v>
+        <v>11.9</v>
       </c>
       <c r="M28">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5475,7 +5475,7 @@
         <v>100</v>
       </c>
       <c r="D29">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>100</v>
@@ -5493,34 +5493,34 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>25</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M29">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5534,7 +5534,7 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
@@ -5552,34 +5552,34 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>25</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K30">
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="M30">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5593,7 +5593,7 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>110</v>
+        <v>91.7</v>
       </c>
       <c r="E31">
         <v>100</v>
@@ -5611,34 +5611,34 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>25</v>
+        <v>61.4</v>
       </c>
       <c r="K31">
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="M31">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>61.4</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5652,7 +5652,7 @@
         <v>28.6</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E32">
         <v>13.3</v>
@@ -5664,40 +5664,40 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5711,7 +5711,7 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>100</v>
@@ -5735,28 +5735,28 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>105</v>
+        <v>95.2</v>
       </c>
       <c r="M33">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5770,7 +5770,7 @@
         <v>100</v>
       </c>
       <c r="D34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>100</v>
@@ -5794,28 +5794,28 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5829,7 +5829,7 @@
         <v>100</v>
       </c>
       <c r="D35">
-        <v>105</v>
+        <v>87.5</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5847,34 +5847,34 @@
         <v>100</v>
       </c>
       <c r="J35">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K35">
         <v>100</v>
       </c>
       <c r="L35">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5888,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="D36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>100</v>
@@ -5903,7 +5903,7 @@
         <v>100</v>
       </c>
       <c r="I36">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="J36">
         <v>100</v>
@@ -5912,28 +5912,28 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5947,7 +5947,7 @@
         <v>100</v>
       </c>
       <c r="D37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>100</v>
@@ -5965,34 +5965,34 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="K37">
         <v>100</v>
       </c>
       <c r="L37">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M37">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>95.5</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6006,7 +6006,7 @@
         <v>100</v>
       </c>
       <c r="D38">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="E38">
         <v>100</v>
@@ -6024,34 +6024,34 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K38">
         <v>100</v>
       </c>
       <c r="L38">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="M38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6065,7 +6065,7 @@
         <v>100</v>
       </c>
       <c r="D39">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>100</v>
@@ -6089,28 +6089,28 @@
         <v>100</v>
       </c>
       <c r="L39">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="M39">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6124,7 +6124,7 @@
         <v>100</v>
       </c>
       <c r="D40">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>100</v>
@@ -6148,28 +6148,28 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M40">
         <v>95</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6183,7 +6183,7 @@
         <v>100</v>
       </c>
       <c r="D41">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E41">
         <v>100</v>
@@ -6201,34 +6201,34 @@
         <v>100</v>
       </c>
       <c r="J41">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K41">
         <v>100</v>
       </c>
       <c r="L41">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M41">
         <v>100</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:19">
@@ -6242,7 +6242,7 @@
         <v>100</v>
       </c>
       <c r="D42">
-        <v>115</v>
+        <v>95.8</v>
       </c>
       <c r="E42">
         <v>100</v>
@@ -6260,34 +6260,34 @@
         <v>100</v>
       </c>
       <c r="J42">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M42">
         <v>100</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6301,7 +6301,7 @@
         <v>100</v>
       </c>
       <c r="D43">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="E43">
         <v>100</v>
@@ -6319,34 +6319,34 @@
         <v>100</v>
       </c>
       <c r="J43">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="K43">
         <v>100</v>
       </c>
       <c r="L43">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="M43">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>97.7</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -849,7 +849,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -917,7 +917,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -926,7 +926,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -935,7 +935,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U5">
         <v>8</v>
@@ -994,7 +994,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1003,7 +1003,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1071,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1080,7 +1080,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1089,7 +1089,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>8</v>
@@ -1148,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1157,7 +1157,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1225,7 +1225,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1234,7 +1234,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1243,7 +1243,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1252,7 +1252,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1302,7 +1302,7 @@
         <v>6</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1311,7 +1311,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1379,7 +1379,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1388,7 +1388,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1397,7 +1397,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1465,7 +1465,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1533,7 +1533,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1542,7 +1542,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1610,7 +1610,7 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1619,7 +1619,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1687,7 +1687,7 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1696,7 +1696,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1705,7 +1705,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15">
         <v>8</v>
@@ -1764,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1773,7 +1773,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1841,7 +1841,7 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1850,7 +1850,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1859,7 +1859,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U17">
         <v>9</v>
@@ -1918,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -1927,7 +1927,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1945,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -1995,7 +1995,7 @@
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2004,7 +2004,7 @@
         <v>-1</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2072,7 +2072,7 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2081,7 +2081,7 @@
         <v>-1</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2149,7 +2149,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2158,7 +2158,7 @@
         <v>-1</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2167,7 +2167,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>9</v>
@@ -2226,7 +2226,7 @@
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2235,7 +2235,7 @@
         <v>-1</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2303,7 +2303,7 @@
         <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2312,7 +2312,7 @@
         <v>-1</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2321,7 +2321,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2380,7 +2380,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2389,7 +2389,7 @@
         <v>-1</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2457,7 +2457,7 @@
         <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2466,7 +2466,7 @@
         <v>-1</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2475,7 +2475,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>7</v>
@@ -2534,7 +2534,7 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2543,7 +2543,7 @@
         <v>-1</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2561,7 +2561,7 @@
         <v>7</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2611,7 +2611,7 @@
         <v>6</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2620,7 +2620,7 @@
         <v>-1</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2688,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2697,7 +2697,7 @@
         <v>-1</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2715,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2765,7 +2765,7 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2774,7 +2774,7 @@
         <v>-1</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2792,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -2842,7 +2842,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -2851,7 +2851,7 @@
         <v>-1</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2919,7 +2919,7 @@
         <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -2928,7 +2928,7 @@
         <v>-1</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -2946,7 +2946,7 @@
         <v>6</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -2996,7 +2996,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3005,7 +3005,7 @@
         <v>-1</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3073,7 +3073,7 @@
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3082,7 +3082,7 @@
         <v>-1</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3150,7 +3150,7 @@
         <v>9</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3159,7 +3159,7 @@
         <v>-1</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3227,7 +3227,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3236,7 +3236,7 @@
         <v>-1</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3245,7 +3245,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3304,7 +3304,7 @@
         <v>9</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3313,7 +3313,7 @@
         <v>-1</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3381,7 +3381,7 @@
         <v>8</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3390,7 +3390,7 @@
         <v>-1</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3408,7 +3408,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3467,7 +3467,7 @@
         <v>-1</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3535,7 +3535,7 @@
         <v>9</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>-1</v>
@@ -3544,7 +3544,7 @@
         <v>-1</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3612,7 +3612,7 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>-1</v>
@@ -3621,7 +3621,7 @@
         <v>-1</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>10</v>
@@ -3689,7 +3689,7 @@
         <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
@@ -3698,7 +3698,7 @@
         <v>-1</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -3707,7 +3707,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>9</v>
@@ -3766,7 +3766,7 @@
         <v>7</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O42">
         <v>-1</v>
@@ -3775,7 +3775,7 @@
         <v>-1</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -3793,7 +3793,7 @@
         <v>7</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>10</v>
@@ -3843,7 +3843,7 @@
         <v>5</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O43">
         <v>-1</v>
@@ -3852,7 +3852,7 @@
         <v>-1</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -3861,7 +3861,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U43">
         <v>8</v>
@@ -4039,7 +4039,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="Q4">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R4">
         <v>95.2</v>
@@ -4098,7 +4098,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R5">
         <v>78.59999999999999</v>
@@ -4511,7 +4511,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R12">
         <v>97.59999999999999</v>
@@ -4806,7 +4806,7 @@
         <v>79.5</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
         <v>85.7</v>
@@ -4983,7 +4983,7 @@
         <v>95.5</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="R20">
         <v>92.90000000000001</v>
@@ -5042,7 +5042,7 @@
         <v>93.2</v>
       </c>
       <c r="Q21">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R21">
         <v>95.2</v>
@@ -5396,7 +5396,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="Q27">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R27">
         <v>76.2</v>
@@ -5446,7 +5446,7 @@
         <v>37.5</v>
       </c>
       <c r="N28">
-        <v>93</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O28">
         <v>90</v>
@@ -5455,7 +5455,7 @@
         <v>65.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="R28">
         <v>11.9</v>
@@ -5682,7 +5682,7 @@
         <v>5</v>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O32">
         <v>14.3</v>
@@ -5691,7 +5691,7 @@
         <v>13.6</v>
       </c>
       <c r="Q32">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="R32">
         <v>7.1</v>
@@ -6163,7 +6163,7 @@
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="R40">
         <v>100</v>
@@ -6281,7 +6281,7 @@
         <v>97.7</v>
       </c>
       <c r="Q42">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="R42">
         <v>100</v>
@@ -6340,7 +6340,7 @@
         <v>97.7</v>
       </c>
       <c r="Q43">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R43">
         <v>83.3</v>
@@ -6508,19 +6508,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>7.5</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -843,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -920,7 +920,7 @@
         <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -938,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>5</v>
@@ -997,7 +997,7 @@
         <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1074,7 +1074,7 @@
         <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1092,7 +1092,7 @@
         <v>7</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1151,7 +1151,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1228,7 +1228,7 @@
         <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1305,7 +1305,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1382,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>6</v>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1613,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1690,7 +1690,7 @@
         <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1767,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1844,7 +1844,7 @@
         <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1862,7 +1862,7 @@
         <v>7</v>
       </c>
       <c r="U17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1921,7 +1921,7 @@
         <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -1998,7 +1998,7 @@
         <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2075,7 +2075,7 @@
         <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2152,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2170,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>7</v>
@@ -2229,7 +2229,7 @@
         <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2247,7 +2247,7 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2306,7 +2306,7 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2383,7 +2383,7 @@
         <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2401,7 +2401,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2460,7 +2460,7 @@
         <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2537,7 +2537,7 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2614,7 +2614,7 @@
         <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2691,7 +2691,7 @@
         <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -2709,7 +2709,7 @@
         <v>5</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2768,7 +2768,7 @@
         <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -2786,7 +2786,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V29">
         <v>6</v>
@@ -2845,7 +2845,7 @@
         <v>6</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P30">
         <v>-1</v>
@@ -2922,7 +2922,7 @@
         <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -2999,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3076,7 +3076,7 @@
         <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3094,7 +3094,7 @@
         <v>10</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V33">
         <v>7</v>
@@ -3153,7 +3153,7 @@
         <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
         <v>-1</v>
@@ -3384,7 +3384,7 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
         <v>-1</v>
@@ -3461,7 +3461,7 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>-1</v>
@@ -3538,7 +3538,7 @@
         <v>9</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>-1</v>
@@ -3633,7 +3633,7 @@
         <v>9</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>6</v>
@@ -3692,7 +3692,7 @@
         <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
         <v>-1</v>
@@ -3710,7 +3710,7 @@
         <v>9</v>
       </c>
       <c r="U41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>7</v>
@@ -3769,7 +3769,7 @@
         <v>8</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P42">
         <v>-1</v>
@@ -3846,7 +3846,7 @@
         <v>5</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P43">
         <v>-1</v>
@@ -3864,7 +3864,7 @@
         <v>6</v>
       </c>
       <c r="U43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V43">
         <v>5</v>
@@ -5449,7 +5449,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="O28">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P28">
         <v>65.90000000000001</v>
@@ -5685,7 +5685,7 @@
         <v>1.3</v>
       </c>
       <c r="O32">
-        <v>14.3</v>
+        <v>8.9</v>
       </c>
       <c r="P32">
         <v>13.6</v>
@@ -5921,7 +5921,7 @@
         <v>100</v>
       </c>
       <c r="O36">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="P36">
         <v>100</v>
@@ -6584,7 +6584,7 @@
         <v>5</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="102">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -263,6 +263,9 @@
     <t>JORGE</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
@@ -287,6 +290,9 @@
     <t>MORA</t>
   </si>
   <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -309,6 +315,9 @@
   </si>
   <si>
     <t>DIEGO</t>
+  </si>
+  <si>
+    <t>CARLOS EDUARDO</t>
   </si>
   <si>
     <t>ROSA</t>
@@ -852,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -929,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1006,7 +1015,7 @@
         <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1024,7 +1033,7 @@
         <v>6</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>7</v>
@@ -1083,7 +1092,7 @@
         <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1101,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1160,7 +1169,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1237,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1255,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>8</v>
@@ -1314,7 +1323,7 @@
         <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1391,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1468,7 +1477,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1486,7 +1495,7 @@
         <v>6</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y12">
         <v>6</v>
@@ -1545,7 +1554,7 @@
         <v>10</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1622,7 +1631,7 @@
         <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1640,7 +1649,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1699,7 +1708,7 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1717,7 +1726,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1776,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1853,7 +1862,7 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1871,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1930,7 +1939,7 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -1948,7 +1957,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2007,7 +2016,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2084,7 +2093,7 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2102,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2161,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2179,7 +2188,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y21">
         <v>7</v>
@@ -2238,7 +2247,7 @@
         <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2256,7 +2265,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2315,7 +2324,7 @@
         <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2333,7 +2342,7 @@
         <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2392,7 +2401,7 @@
         <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2410,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2469,7 +2478,7 @@
         <v>6</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2546,7 +2555,7 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2564,7 +2573,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2623,7 +2632,7 @@
         <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2641,7 +2650,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y27">
         <v>7</v>
@@ -2700,7 +2709,7 @@
         <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2777,7 +2786,7 @@
         <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2795,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="X29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2854,7 +2863,7 @@
         <v>7</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -2931,7 +2940,7 @@
         <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -2949,7 +2958,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>5</v>
@@ -3008,7 +3017,7 @@
         <v>5</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3085,7 +3094,7 @@
         <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3103,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>8</v>
@@ -3162,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3239,7 +3248,7 @@
         <v>9</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3316,7 +3325,7 @@
         <v>10</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3334,7 +3343,7 @@
         <v>10</v>
       </c>
       <c r="X36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3393,7 +3402,7 @@
         <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3470,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3488,7 +3497,7 @@
         <v>7</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y38">
         <v>8</v>
@@ -3547,7 +3556,7 @@
         <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3624,7 +3633,7 @@
         <v>6</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3642,7 +3651,7 @@
         <v>8</v>
       </c>
       <c r="X40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y40">
         <v>7</v>
@@ -3701,7 +3710,7 @@
         <v>8</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3719,7 +3728,7 @@
         <v>9</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>8</v>
@@ -3778,7 +3787,7 @@
         <v>5</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -3855,7 +3864,7 @@
         <v>5</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4042,7 +4051,7 @@
         <v>95.8</v>
       </c>
       <c r="R4">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -4101,7 +4110,7 @@
         <v>93.8</v>
       </c>
       <c r="R5">
-        <v>78.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4160,7 +4169,7 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="S6">
         <v>92.5</v>
@@ -4219,7 +4228,7 @@
         <v>100</v>
       </c>
       <c r="R7">
-        <v>92.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S7">
         <v>87.5</v>
@@ -4278,7 +4287,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4337,7 +4346,7 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4396,7 +4405,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>92.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S10">
         <v>97.5</v>
@@ -4455,7 +4464,7 @@
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>97.5</v>
@@ -4514,7 +4523,7 @@
         <v>93.8</v>
       </c>
       <c r="R12">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
         <v>97.5</v>
@@ -4573,7 +4582,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -4632,7 +4641,7 @@
         <v>100</v>
       </c>
       <c r="R14">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S14">
         <v>97.5</v>
@@ -4691,7 +4700,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>83.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S15">
         <v>97.5</v>
@@ -4750,7 +4759,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>97.5</v>
@@ -4809,7 +4818,7 @@
         <v>93.8</v>
       </c>
       <c r="R17">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
       <c r="S17">
         <v>97.5</v>
@@ -4868,7 +4877,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="S18">
         <v>97.5</v>
@@ -4986,7 +4995,7 @@
         <v>93.8</v>
       </c>
       <c r="R20">
-        <v>92.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S20">
         <v>97.5</v>
@@ -5045,7 +5054,7 @@
         <v>95.8</v>
       </c>
       <c r="R21">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="S21">
         <v>97.5</v>
@@ -5104,7 +5113,7 @@
         <v>100</v>
       </c>
       <c r="R22">
-        <v>85.7</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="S22">
         <v>85</v>
@@ -5163,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>88.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S23">
         <v>97.5</v>
@@ -5222,7 +5231,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="S24">
         <v>92.5</v>
@@ -5281,7 +5290,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S25">
         <v>90</v>
@@ -5340,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="R26">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S26">
         <v>97.5</v>
@@ -5399,7 +5408,7 @@
         <v>95.8</v>
       </c>
       <c r="R27">
-        <v>76.2</v>
+        <v>79.7</v>
       </c>
       <c r="S27">
         <v>95</v>
@@ -5458,7 +5467,7 @@
         <v>83.3</v>
       </c>
       <c r="R28">
-        <v>11.9</v>
+        <v>23.4</v>
       </c>
       <c r="S28">
         <v>37.5</v>
@@ -5517,7 +5526,7 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S29">
         <v>92.5</v>
@@ -5576,7 +5585,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>66.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S30">
         <v>90</v>
@@ -5635,7 +5644,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>85.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S31">
         <v>87.5</v>
@@ -5694,7 +5703,7 @@
         <v>4.2</v>
       </c>
       <c r="R32">
-        <v>7.1</v>
+        <v>4.7</v>
       </c>
       <c r="S32">
         <v>5</v>
@@ -5753,7 +5762,7 @@
         <v>100</v>
       </c>
       <c r="R33">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="S33">
         <v>90</v>
@@ -5871,7 +5880,7 @@
         <v>100</v>
       </c>
       <c r="R35">
-        <v>92.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="S35">
         <v>95</v>
@@ -5930,7 +5939,7 @@
         <v>100</v>
       </c>
       <c r="R36">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6048,7 +6057,7 @@
         <v>100</v>
       </c>
       <c r="R38">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S38">
         <v>95</v>
@@ -6107,7 +6116,7 @@
         <v>100</v>
       </c>
       <c r="R39">
-        <v>95.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S39">
         <v>97.5</v>
@@ -6166,7 +6175,7 @@
         <v>95.8</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S40">
         <v>95</v>
@@ -6225,7 +6234,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -6284,7 +6293,7 @@
         <v>91.7</v>
       </c>
       <c r="R42">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="S42">
         <v>100</v>
@@ -6343,7 +6352,7 @@
         <v>97.90000000000001</v>
       </c>
       <c r="R43">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
       <c r="S43">
         <v>80</v>
@@ -6435,7 +6444,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>65</v>
@@ -6456,7 +6465,7 @@
         <v>20</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6467,7 +6476,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>66</v>
@@ -6476,19 +6485,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>82.5</v>
+        <v>80</v>
       </c>
       <c r="G4" s="2">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6634,7 +6643,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6672,10 +6681,10 @@
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6695,16 +6704,16 @@
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6718,10 +6727,10 @@
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6741,16 +6750,16 @@
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6764,10 +6773,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6787,16 +6796,16 @@
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6810,10 +6819,10 @@
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6833,16 +6842,16 @@
         <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6856,10 +6865,10 @@
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6879,10 +6888,10 @@
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6902,10 +6911,10 @@
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6919,19 +6928,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920070</v>
+        <v>22330051920380</v>
       </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
         <v>65</v>
@@ -6942,24 +6951,47 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920317</v>
+        <v>22330051920070</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920317</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
         <v>75</v>
       </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14">
+      <c r="D15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2ARHM - Estadisticos 20222.xlsx
+++ b/grupos/2ARHM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -242,27 +242,30 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -272,51 +275,69 @@
     <t>ORTEGA</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CHIMALHUA</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>MORA</t>
   </si>
   <si>
+    <t>SILVA</t>
+  </si>
+  <si>
     <t>ORTIZ</t>
   </si>
   <si>
     <t>TEXOCO</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>DANIELA</t>
   </si>
   <si>
+    <t>DANA PAOLA</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
+    <t>SALMA AISHA</t>
+  </si>
+  <si>
     <t>CLAUDIA PAOLA</t>
   </si>
   <si>
-    <t>JIMENA</t>
-  </si>
-  <si>
-    <t>DANA PAOLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>DANIEL ELEAZAR</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>HANNY YUSETH</t>
+  </si>
+  <si>
     <t>CARLOS EDUARDO</t>
   </si>
   <si>
@@ -324,6 +345,9 @@
   </si>
   <si>
     <t>JESUS ALEJANDRO</t>
+  </si>
+  <si>
+    <t>MELANIE SOFIA</t>
   </si>
 </sst>
 </file>
@@ -855,7 +879,7 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>9</v>
@@ -864,7 +888,7 @@
         <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>8</v>
@@ -873,7 +897,7 @@
         <v>9</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -932,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>6</v>
@@ -941,7 +965,7 @@
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -1009,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>6</v>
@@ -1018,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1036,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1086,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
         <v>6</v>
@@ -1095,7 +1119,7 @@
         <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T7">
         <v>7</v>
@@ -1113,7 +1137,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1163,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>10</v>
@@ -1172,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1240,7 +1264,7 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -1249,7 +1273,7 @@
         <v>5</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1258,7 +1282,7 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1317,7 +1341,7 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>10</v>
@@ -1326,7 +1350,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1335,7 +1359,7 @@
         <v>8</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>9</v>
@@ -1394,7 +1418,7 @@
         <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -1403,7 +1427,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1412,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W11">
         <v>8</v>
@@ -1471,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>7</v>
@@ -1480,7 +1504,7 @@
         <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>7</v>
@@ -1548,7 +1572,7 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>10</v>
@@ -1557,7 +1581,7 @@
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
@@ -1625,7 +1649,7 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>6</v>
@@ -1634,7 +1658,7 @@
         <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>7</v>
@@ -1702,7 +1726,7 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q15">
         <v>8</v>
@@ -1711,7 +1735,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>7</v>
@@ -1720,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1779,7 +1803,7 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1788,7 +1812,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1797,7 +1821,7 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>10</v>
@@ -1856,7 +1880,7 @@
         <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>9</v>
@@ -1865,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1883,7 +1907,7 @@
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1933,7 +1957,7 @@
         <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
         <v>5</v>
@@ -1942,7 +1966,7 @@
         <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>7</v>
@@ -2010,7 +2034,7 @@
         <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
         <v>5</v>
@@ -2019,7 +2043,7 @@
         <v>5</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>5</v>
@@ -2087,7 +2111,7 @@
         <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q20">
         <v>9</v>
@@ -2096,7 +2120,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2105,7 +2129,7 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2164,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>8</v>
@@ -2173,7 +2197,7 @@
         <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2182,7 +2206,7 @@
         <v>8</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2191,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2241,7 +2265,7 @@
         <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -2250,7 +2274,7 @@
         <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2318,7 +2342,7 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
         <v>9</v>
@@ -2327,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2336,7 +2360,7 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2395,7 +2419,7 @@
         <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>8</v>
@@ -2404,7 +2428,7 @@
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2413,7 +2437,7 @@
         <v>9</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>8</v>
@@ -2472,7 +2496,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>6</v>
@@ -2481,7 +2505,7 @@
         <v>5</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2499,7 +2523,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2549,7 +2573,7 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>8</v>
@@ -2558,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2567,7 +2591,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>9</v>
@@ -2576,7 +2600,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2626,7 +2650,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>7</v>
@@ -2635,7 +2659,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>6</v>
@@ -2644,7 +2668,7 @@
         <v>8</v>
       </c>
       <c r="V27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -2703,7 +2727,7 @@
         <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
         <v>7</v>
@@ -2712,7 +2736,7 @@
         <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>5</v>
@@ -2780,7 +2804,7 @@
         <v>5</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>5</v>
@@ -2789,7 +2813,7 @@
         <v>5</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -2798,7 +2822,7 @@
         <v>7</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2807,7 +2831,7 @@
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2857,7 +2881,7 @@
         <v>8</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>7</v>
@@ -2866,7 +2890,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
         <v>7</v>
@@ -2884,7 +2908,7 @@
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2934,7 +2958,7 @@
         <v>7</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>7</v>
@@ -2943,7 +2967,7 @@
         <v>5</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>7</v>
@@ -2952,7 +2976,7 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -2961,7 +2985,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3011,7 +3035,7 @@
         <v>5</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
         <v>5</v>
@@ -3020,7 +3044,7 @@
         <v>5</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T32">
         <v>5</v>
@@ -3088,7 +3112,7 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>10</v>
@@ -3097,7 +3121,7 @@
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3106,7 +3130,7 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
         <v>10</v>
@@ -3165,7 +3189,7 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>10</v>
@@ -3174,7 +3198,7 @@
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
         <v>10</v>
@@ -3242,7 +3266,7 @@
         <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q35">
         <v>9</v>
@@ -3251,7 +3275,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3260,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3319,7 +3343,7 @@
         <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>10</v>
@@ -3328,7 +3352,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3337,7 +3361,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>10</v>
@@ -3396,7 +3420,7 @@
         <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>9</v>
@@ -3405,7 +3429,7 @@
         <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3423,7 +3447,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3473,7 +3497,7 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q38">
         <v>8</v>
@@ -3482,7 +3506,7 @@
         <v>5</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3491,7 +3515,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3550,7 +3574,7 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
         <v>10</v>
@@ -3559,7 +3583,7 @@
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3627,7 +3651,7 @@
         <v>7</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q40">
         <v>6</v>
@@ -3636,7 +3660,7 @@
         <v>7</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3704,7 +3728,7 @@
         <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q41">
         <v>8</v>
@@ -3713,7 +3737,7 @@
         <v>5</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3722,7 +3746,7 @@
         <v>8</v>
       </c>
       <c r="V41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W41">
         <v>9</v>
@@ -3781,7 +3805,7 @@
         <v>9</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q42">
         <v>5</v>
@@ -3790,7 +3814,7 @@
         <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -3799,7 +3823,7 @@
         <v>9</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W42">
         <v>8</v>
@@ -3808,7 +3832,7 @@
         <v>10</v>
       </c>
       <c r="Y42">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:25">
@@ -3858,7 +3882,7 @@
         <v>5</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>5</v>
@@ -3867,7 +3891,7 @@
         <v>5</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T43">
         <v>6</v>
@@ -4045,7 +4069,7 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q4">
         <v>95.8</v>
@@ -4104,7 +4128,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>88.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="Q5">
         <v>93.8</v>
@@ -4113,7 +4137,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -4163,7 +4187,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4172,7 +4196,7 @@
         <v>95.3</v>
       </c>
       <c r="S6">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4222,7 +4246,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -4231,7 +4255,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S7">
-        <v>87.5</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4281,7 +4305,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -4340,7 +4364,7 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="Q9">
         <v>100</v>
@@ -4399,7 +4423,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4408,7 +4432,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S10">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4458,7 +4482,7 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -4467,7 +4491,7 @@
         <v>95.3</v>
       </c>
       <c r="S11">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4517,7 +4541,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="Q12">
         <v>93.8</v>
@@ -4526,7 +4550,7 @@
         <v>93.8</v>
       </c>
       <c r="S12">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4576,7 +4600,7 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -4635,7 +4659,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -4644,7 +4668,7 @@
         <v>87.5</v>
       </c>
       <c r="S14">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4694,7 +4718,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -4703,7 +4727,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S15">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4762,7 +4786,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S16">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4812,7 +4836,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Q17">
         <v>93.8</v>
@@ -4821,7 +4845,7 @@
         <v>87.5</v>
       </c>
       <c r="S17">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4871,7 +4895,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4880,7 +4904,7 @@
         <v>87.5</v>
       </c>
       <c r="S18">
-        <v>97.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4989,7 +5013,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>95.5</v>
+        <v>92.2</v>
       </c>
       <c r="Q20">
         <v>93.8</v>
@@ -4998,7 +5022,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S20">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -5048,7 +5072,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="Q21">
         <v>95.8</v>
@@ -5057,7 +5081,7 @@
         <v>93.8</v>
       </c>
       <c r="S21">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -5107,7 +5131,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>86.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -5116,7 +5140,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="S22">
-        <v>85</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -5166,7 +5190,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -5175,7 +5199,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="S23">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -5234,7 +5258,7 @@
         <v>93.8</v>
       </c>
       <c r="S24">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5284,7 +5308,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -5293,7 +5317,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S25">
-        <v>90</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5352,7 +5376,7 @@
         <v>95.3</v>
       </c>
       <c r="S26">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5402,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>88.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="Q27">
         <v>95.8</v>
@@ -5411,7 +5435,7 @@
         <v>79.7</v>
       </c>
       <c r="S27">
-        <v>95</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5461,7 +5485,7 @@
         <v>93.8</v>
       </c>
       <c r="P28">
-        <v>65.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q28">
         <v>83.3</v>
@@ -5470,7 +5494,7 @@
         <v>23.4</v>
       </c>
       <c r="S28">
-        <v>37.5</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5520,7 +5544,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>65.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -5529,7 +5553,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S29">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5579,7 +5603,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>65.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -5588,7 +5612,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5638,7 +5662,7 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>61.4</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -5647,7 +5671,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S31">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5697,7 +5721,7 @@
         <v>8.9</v>
       </c>
       <c r="P32">
-        <v>13.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q32">
         <v>4.2</v>
@@ -5706,7 +5730,7 @@
         <v>4.7</v>
       </c>
       <c r="S32">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5756,7 +5780,7 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q33">
         <v>100</v>
@@ -5765,7 +5789,7 @@
         <v>93.8</v>
       </c>
       <c r="S33">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5874,7 +5898,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>88.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -5883,7 +5907,7 @@
         <v>95.3</v>
       </c>
       <c r="S35">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5992,7 +6016,7 @@
         <v>100</v>
       </c>
       <c r="P37">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="Q37">
         <v>100</v>
@@ -6001,7 +6025,7 @@
         <v>100</v>
       </c>
       <c r="S37">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -6051,7 +6075,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>86.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6060,7 +6084,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="S38">
-        <v>95</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -6119,7 +6143,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S39">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -6169,7 +6193,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q40">
         <v>95.8</v>
@@ -6178,7 +6202,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S40">
-        <v>95</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="41" spans="1:19">
@@ -6228,7 +6252,7 @@
         <v>100</v>
       </c>
       <c r="P41">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
       <c r="Q41">
         <v>100</v>
@@ -6287,7 +6311,7 @@
         <v>100</v>
       </c>
       <c r="P42">
-        <v>97.7</v>
+        <v>92.2</v>
       </c>
       <c r="Q42">
         <v>91.7</v>
@@ -6296,7 +6320,7 @@
         <v>95.3</v>
       </c>
       <c r="S42">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:19">
@@ -6346,7 +6370,7 @@
         <v>100</v>
       </c>
       <c r="P43">
-        <v>97.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q43">
         <v>97.90000000000001</v>
@@ -6355,7 +6379,7 @@
         <v>82.8</v>
       </c>
       <c r="S43">
-        <v>80</v>
+        <v>78.09999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6421,19 +6445,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6485,19 +6509,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="G4" s="2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6643,7 +6667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6675,16 +6699,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920061</v>
+        <v>22330051920054</v>
       </c>
       <c r="B2" t="s">
         <v>74</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -6698,16 +6722,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920061</v>
+        <v>22330051920054</v>
       </c>
       <c r="B3" t="s">
         <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -6721,16 +6745,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -6744,16 +6768,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920212</v>
+        <v>22330051920061</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -6767,16 +6791,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920068</v>
+        <v>22330051920071</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -6790,16 +6814,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920068</v>
+        <v>22330051920071</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -6813,16 +6837,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920071</v>
+        <v>22330051920058</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -6836,22 +6860,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920071</v>
+        <v>22330051920062</v>
       </c>
       <c r="B9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6859,16 +6883,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920054</v>
+        <v>22330051920212</v>
       </c>
       <c r="B10" t="s">
         <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -6888,10 +6912,10 @@
         <v>79</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -6911,10 +6935,10 @@
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -6928,22 +6952,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920380</v>
+        <v>22230030070114</v>
       </c>
       <c r="B13" t="s">
         <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -6951,22 +6975,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920070</v>
+        <v>22330051920380</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -6974,24 +6998,70 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920317</v>
+        <v>22330051920070</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920317</v>
+      </c>
+      <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920079</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>109</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>
